--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{653074E1-AC68-42CB-866E-2162B1BA8677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8543CC8A-953E-45DD-A8CA-D24C2F232238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1410" windowWidth="16305" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -905,9 +905,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -954,7 +954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>105</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>114</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>122</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>149</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>154</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>157</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>163</v>
       </c>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4696433A-B9D1-4233-BFCE-44731ACF5073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{012DA0C2-48EF-4749-A953-FDAD6C3BE711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="170">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,39 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>04/07/2026 7:34:13 PM</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Hunter McDowell</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Passengers, Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>3175 Tanglewood Lane, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
+  </si>
+  <si>
     <t>04/02/2026 6:07:12 AM</t>
   </si>
   <si>
@@ -71,21 +104,12 @@
     <t>Larry Richardson</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Harsh Brake</t>
   </si>
   <si>
     <t>Wet Road, Moderate Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>South Grant Avenue, Odessa, TX, 79761</t>
   </si>
   <si>
@@ -167,6 +191,9 @@
     <t>Construction, Pedestrians, Moderate Traffic</t>
   </si>
   <si>
+    <t>Coached</t>
+  </si>
+  <si>
     <t>I 20, Warfield, TX, 79711</t>
   </si>
   <si>
@@ -248,9 +275,6 @@
     <t>Inattentive Driving</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>Shakespeare Road, Odessa, TX, 79761</t>
   </si>
   <si>
@@ -377,9 +401,6 @@
     <t>02/09/2026 5:58:32 PM</t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>I 20-E Business, Midland, TX, 79712</t>
   </si>
   <si>
@@ -504,27 +525,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bfc4-abe8-51f8-b58d-cb0531632c98</t>
-  </si>
-  <si>
-    <t>01/11/2026 8:24:57 PM</t>
-  </si>
-  <si>
-    <t>800 South Texas Avenue, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b005-5489-5154-a7fc-8d434f2f9738</t>
-  </si>
-  <si>
-    <t>01/08/2026 2:10:50 PM</t>
-  </si>
-  <si>
-    <t>813 South Texas Avenue, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459f3b-bce6-5095-9de6-6668f379bfd5</t>
   </si>
 </sst>
 </file>
@@ -901,7 +901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -992,33 +992,33 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -1027,11 +1027,11 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
       <c r="L3" t="s">
         <v>18</v>
       </c>
@@ -1039,21 +1039,21 @@
         <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1062,10 +1062,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1074,10 +1074,10 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -1089,18 +1089,18 @@
         <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -1109,10 +1109,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1121,10 +1121,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1133,21 +1133,21 @@
         <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1156,7 +1156,7 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
         <v>49</v>
@@ -1203,22 +1203,22 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
         <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1227,21 +1227,21 @@
         <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1250,10 +1250,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1262,10 +1262,10 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1274,21 +1274,21 @@
         <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1297,10 +1297,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1309,10 +1309,10 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>18</v>
@@ -1321,21 +1321,21 @@
         <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1344,28 +1344,28 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
         <v>18</v>
@@ -1379,10 +1379,10 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1391,45 +1391,45 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="N11" t="s">
         <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1438,45 +1438,45 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
         <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1485,45 +1485,45 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="N13" t="s">
         <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1532,22 +1532,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1556,21 +1556,21 @@
         <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1579,10 +1579,10 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1591,10 +1591,10 @@
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1603,21 +1603,21 @@
         <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="O15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1626,22 +1626,22 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -1653,18 +1653,18 @@
         <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1673,22 +1673,22 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I17" t="s">
         <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -1700,18 +1700,18 @@
         <v>18</v>
       </c>
       <c r="O17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1720,22 +1720,22 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -1747,12 +1747,12 @@
         <v>18</v>
       </c>
       <c r="O18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
@@ -1767,22 +1767,22 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
         <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -1794,18 +1794,18 @@
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1814,22 +1814,22 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K20" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="L20" t="s">
         <v>18</v>
@@ -1838,21 +1838,21 @@
         <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -1861,22 +1861,22 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I21" t="s">
         <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K21" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s">
         <v>18</v>
@@ -1885,21 +1885,21 @@
         <v>18</v>
       </c>
       <c r="N21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -1908,22 +1908,22 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I22" t="s">
         <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L22" t="s">
         <v>18</v>
@@ -1932,21 +1932,21 @@
         <v>18</v>
       </c>
       <c r="N22" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="O22" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -1955,22 +1955,22 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L23" t="s">
         <v>18</v>
@@ -1982,18 +1982,18 @@
         <v>18</v>
       </c>
       <c r="O23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -2002,22 +2002,22 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L24" t="s">
         <v>18</v>
@@ -2029,18 +2029,18 @@
         <v>18</v>
       </c>
       <c r="O24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -2049,22 +2049,22 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
       <c r="J25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K25" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L25" t="s">
         <v>18</v>
@@ -2076,18 +2076,18 @@
         <v>18</v>
       </c>
       <c r="O25" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -2096,22 +2096,22 @@
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K26" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="L26" t="s">
         <v>18</v>
@@ -2123,18 +2123,18 @@
         <v>18</v>
       </c>
       <c r="O26" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -2143,22 +2143,22 @@
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s">
         <v>18</v>
@@ -2170,18 +2170,18 @@
         <v>18</v>
       </c>
       <c r="O27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -2190,22 +2190,22 @@
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s">
         <v>18</v>
@@ -2217,18 +2217,18 @@
         <v>18</v>
       </c>
       <c r="O28" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -2237,10 +2237,10 @@
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
@@ -2249,10 +2249,10 @@
         <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K29" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="L29" t="s">
         <v>18</v>
@@ -2264,53 +2264,6 @@
         <v>18</v>
       </c>
       <c r="O29" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
-        <v>30</v>
-      </c>
-      <c r="G30" t="s">
-        <v>63</v>
-      </c>
-      <c r="H30" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" t="s">
-        <v>167</v>
-      </c>
-      <c r="K30" t="s">
-        <v>168</v>
-      </c>
-      <c r="L30" t="s">
-        <v>18</v>
-      </c>
-      <c r="M30" t="s">
-        <v>18</v>
-      </c>
-      <c r="N30" t="s">
-        <v>18</v>
-      </c>
-      <c r="O30" t="s">
         <v>169</v>
       </c>
     </row>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{012DA0C2-48EF-4749-A953-FDAD6C3BE711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7972BA7E-2335-4657-A36B-29A679AB7793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="154">
   <si>
     <t>Time</t>
   </si>
@@ -477,54 +477,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d871-87a8-5117-8550-947725cb7b47</t>
-  </si>
-  <si>
-    <t>01/16/2026 5:24:56 PM</t>
-  </si>
-  <si>
-    <t>5001 Highway 80, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c920-5113-5b6b-bc0c-87d9872eb59d</t>
-  </si>
-  <si>
-    <t>01/15/2026 10:18:40 AM</t>
-  </si>
-  <si>
-    <t>TX 115, 13.9 mi NE Andrews, Andrews County, TX</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c273-af2e-53a8-9500-4071973a48a0</t>
-  </si>
-  <si>
-    <t>01/14/2026 9:54:45 PM</t>
-  </si>
-  <si>
-    <t>Moderate Traffic, Night</t>
-  </si>
-  <si>
-    <t>I 20, Odessa, TX, 79763</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bfca-9f39-5d9f-8bd5-66976bd4e93b</t>
-  </si>
-  <si>
-    <t>01/14/2026 9:48:15 PM</t>
-  </si>
-  <si>
-    <t>Interstate Highway 20 Service Drive, Penwell, TX, 79776</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bfc4-abe8-51f8-b58d-cb0531632c98</t>
   </si>
 </sst>
 </file>
@@ -901,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2079,194 +2031,6 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s">
-        <v>155</v>
-      </c>
-      <c r="K26" t="s">
-        <v>139</v>
-      </c>
-      <c r="L26" t="s">
-        <v>18</v>
-      </c>
-      <c r="M26" t="s">
-        <v>18</v>
-      </c>
-      <c r="N26" t="s">
-        <v>18</v>
-      </c>
-      <c r="O26" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" t="s">
-        <v>58</v>
-      </c>
-      <c r="I27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s">
-        <v>158</v>
-      </c>
-      <c r="K27" t="s">
-        <v>159</v>
-      </c>
-      <c r="L27" t="s">
-        <v>18</v>
-      </c>
-      <c r="M27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N27" t="s">
-        <v>18</v>
-      </c>
-      <c r="O27" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" t="s">
-        <v>162</v>
-      </c>
-      <c r="H28" t="s">
-        <v>58</v>
-      </c>
-      <c r="I28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" t="s">
-        <v>163</v>
-      </c>
-      <c r="K28" t="s">
-        <v>164</v>
-      </c>
-      <c r="L28" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N28" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" t="s">
-        <v>167</v>
-      </c>
-      <c r="K29" t="s">
-        <v>168</v>
-      </c>
-      <c r="L29" t="s">
-        <v>18</v>
-      </c>
-      <c r="M29" t="s">
-        <v>18</v>
-      </c>
-      <c r="N29" t="s">
-        <v>18</v>
-      </c>
-      <c r="O29" t="s">
-        <v>169</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7972BA7E-2335-4657-A36B-29A679AB7793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06DAAE65-0EF2-4A53-835B-C44B42D1E0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="142">
   <si>
     <t>Time</t>
   </si>
@@ -441,42 +441,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445108f-b64d-5cf6-bbf5-479f328dd4c6</t>
-  </si>
-  <si>
-    <t>01/22/2026 8:14:32 AM</t>
-  </si>
-  <si>
-    <t>3217 Rocky Lane Road, Odessa, TX, 79762</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e60e-8e4f-58e6-ab5a-9ff87cafdcc4</t>
-  </si>
-  <si>
-    <t>01/21/2026 6:15:39 AM</t>
-  </si>
-  <si>
-    <t>I 20, 8.6 mi ENE Midland, Midland County, TX, 79702</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e07b-5c39-5596-9031-e354b819ae44</t>
-  </si>
-  <si>
-    <t>01/19/2026 4:47:57 PM</t>
-  </si>
-  <si>
-    <t>I 20, 4.1 mi SE West Odessa, Ector County, TX, 79763</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d871-87a8-5117-8550-947725cb7b47</t>
   </si>
 </sst>
 </file>
@@ -853,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1890,147 +1854,6 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>143</v>
-      </c>
-      <c r="K23" t="s">
-        <v>144</v>
-      </c>
-      <c r="L23" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" t="s">
-        <v>58</v>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s">
-        <v>147</v>
-      </c>
-      <c r="K24" t="s">
-        <v>148</v>
-      </c>
-      <c r="L24" t="s">
-        <v>18</v>
-      </c>
-      <c r="M24" t="s">
-        <v>18</v>
-      </c>
-      <c r="N24" t="s">
-        <v>18</v>
-      </c>
-      <c r="O24" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" t="s">
-        <v>58</v>
-      </c>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s">
-        <v>151</v>
-      </c>
-      <c r="K25" t="s">
-        <v>152</v>
-      </c>
-      <c r="L25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N25" t="s">
-        <v>18</v>
-      </c>
-      <c r="O25" t="s">
-        <v>153</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06DAAE65-0EF2-4A53-835B-C44B42D1E0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6F13B6C-532F-489E-9068-4AEAE8E651AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="2895" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="100">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,42 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>05/01/2026 2:14:13 PM</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Leonard Ramirez</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>I 20-E Business, Midland, TX, 79712</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e4f6-81e7-5c75-8318-c6dfd58c5b0c</t>
+  </si>
+  <si>
     <t>04/07/2026 7:34:13 PM</t>
   </si>
   <si>
@@ -71,21 +107,12 @@
     <t>Hunter McDowell</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
     <t>Passengers, Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>3175 Tanglewood Lane, Odessa, TX, 79762</t>
   </si>
   <si>
@@ -104,9 +131,6 @@
     <t>Larry Richardson</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Wet Road, Moderate Traffic, Night</t>
   </si>
   <si>
@@ -179,7 +203,25 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
   </si>
   <si>
-    <t>03/26/2026 1:22:56 PM</t>
+    <t>03/22/2026 10:09:28 PM</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>4305 North Grandview Avenue, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544518ab-3d01-5bf0-b82b-40d74389918d</t>
+  </si>
+  <si>
+    <t>03/13/2026 9:33:47 AM</t>
   </si>
   <si>
     <t>583</t>
@@ -188,105 +230,36 @@
     <t>Rodney Salcido</t>
   </si>
   <si>
-    <t>Construction, Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>I 20, Warfield, TX, 79711</t>
+    <t>East Interstate 20, 5.4 mi ENE Midland, Midland County, TX, 79702</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e79e-255b-5dbc-baaf-e9de51a814a8</t>
+  </si>
+  <si>
+    <t>03/11/2026 11:18:32 AM</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Fabian Velasco</t>
+  </si>
+  <si>
+    <t>7606 Tres Hermanas Boulevard, Odessa, TX, 79765</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
-  </si>
-  <si>
-    <t>03/22/2026 10:09:28 PM</t>
-  </si>
-  <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Leonard Ramirez</t>
-  </si>
-  <si>
-    <t>Wet Road, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>4305 North Grandview Avenue, Odessa, TX, 79762</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544518ab-3d01-5bf0-b82b-40d74389918d</t>
-  </si>
-  <si>
-    <t>03/13/2026 9:33:47 AM</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>East Interstate 20, 5.4 mi ENE Midland, Midland County, TX, 79702</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e79e-255b-5dbc-baaf-e9de51a814a8</t>
-  </si>
-  <si>
-    <t>03/11/2026 11:18:32 AM</t>
-  </si>
-  <si>
-    <t>606</t>
-  </si>
-  <si>
-    <t>Fabian Velasco</t>
-  </si>
-  <si>
-    <t>7606 Tres Hermanas Boulevard, Odessa, TX, 79765</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb1-578c-5827-804c-7990c6190630</t>
   </si>
   <si>
-    <t>03/03/2026 7:19:10 PM</t>
-  </si>
-  <si>
-    <t>517</t>
-  </si>
-  <si>
-    <t>Nathan Roe</t>
-  </si>
-  <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
-    <t>Shakespeare Road, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b66d-6c38-58b4-9408-70137dcb76a1</t>
-  </si>
-  <si>
     <t>03/02/2026 3:37:09 PM</t>
   </si>
   <si>
@@ -302,19 +275,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b07b-cced-5497-a51f-46c4359728ac</t>
   </si>
   <si>
-    <t>02/27/2026 6:34:29 PM</t>
-  </si>
-  <si>
-    <t>US 87, 26.0 mi NW San Angelo, Sterling County, TX</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a1ab-12c0-5caf-b2f6-baf9d4e12298</t>
-  </si>
-  <si>
-    <t>02/21/2026 3:58:28 PM</t>
+    <t>02/20/2026 6:02:32 PM</t>
   </si>
   <si>
     <t>607</t>
@@ -323,18 +284,6 @@
     <t>James Jenkins</t>
   </si>
   <si>
-    <t>209 West 8th Street, Odessa, TX, 79763</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458236-1570-5cb7-8371-272bd8f12c91</t>
-  </si>
-  <si>
-    <t>02/20/2026 6:02:32 PM</t>
-  </si>
-  <si>
     <t>Harsh Turn</t>
   </si>
   <si>
@@ -359,88 +308,13 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457ba8-ebfa-5b43-9827-b1e3862a826a</t>
   </si>
   <si>
-    <t>02/13/2026 3:38:17 PM</t>
-  </si>
-  <si>
-    <t>591</t>
-  </si>
-  <si>
-    <t>Interstate Highway 20 Service Road, 17.9 mi WSW Big Spring, Martin County, TX, 79782</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544558f0-bcf4-5e11-83e9-a1959020f984</t>
-  </si>
-  <si>
-    <t>02/12/2026 7:09:16 PM</t>
-  </si>
-  <si>
-    <t>TX 115, 3.2 mi NE Kermit, Winkler County, TX, 79745</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445548b-8833-5d53-90fe-30f4d3a2ec96</t>
-  </si>
-  <si>
-    <t>02/11/2026 5:15:27 PM</t>
-  </si>
-  <si>
-    <t>1740 South Dixie Boulevard, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454efc-fa63-59f7-82ae-fbd6da2d6836</t>
-  </si>
-  <si>
     <t>02/09/2026 5:58:32 PM</t>
   </si>
   <si>
-    <t>I 20-E Business, Midland, TX, 79712</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544544d7-b107-5005-9aaa-fbe04e586345</t>
-  </si>
-  <si>
-    <t>02/01/2026 3:52:36 AM</t>
-  </si>
-  <si>
-    <t>Crash</t>
-  </si>
-  <si>
-    <t>2667 I 20 BUS, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>2.15</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445189e-58ee-5dd1-a04c-22ec1544ee4b</t>
-  </si>
-  <si>
-    <t>01/30/2026 2:19:39 PM</t>
-  </si>
-  <si>
-    <t>515</t>
-  </si>
-  <si>
-    <t>830 West University Boulevard, Odessa, TX, 79764</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445108f-b64d-5cf6-bbf5-479f328dd4c6</t>
   </si>
 </sst>
 </file>
@@ -817,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -908,21 +782,21 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -931,10 +805,10 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -943,10 +817,10 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -955,7 +829,7 @@
         <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -978,10 +852,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -990,11 +864,11 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
       <c r="L4" t="s">
         <v>18</v>
       </c>
@@ -1002,21 +876,21 @@
         <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="O4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -1025,10 +899,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1037,10 +911,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1052,18 +926,18 @@
         <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1072,10 +946,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1084,10 +958,10 @@
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1096,21 +970,21 @@
         <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1119,45 +993,45 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
         <v>57</v>
       </c>
       <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>58</v>
       </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>59</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
         <v>60</v>
       </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>61</v>
-      </c>
-      <c r="O7" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1166,10 +1040,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1178,33 +1052,33 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" t="s">
         <v>67</v>
-      </c>
-      <c r="K8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
-        <v>69</v>
-      </c>
-      <c r="O8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1213,10 +1087,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1225,33 +1099,33 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
         <v>73</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
         <v>74</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>75</v>
-      </c>
-      <c r="O9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
         <v>77</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1260,10 +1134,10 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -1272,33 +1146,33 @@
         <v>18</v>
       </c>
       <c r="J10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
         <v>80</v>
-      </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1307,45 +1181,45 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
         <v>85</v>
-      </c>
-      <c r="G11" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" t="s">
-        <v>87</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>88</v>
-      </c>
-      <c r="N11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1354,10 +1228,10 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -1366,33 +1240,33 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
         <v>92</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" t="s">
         <v>93</v>
-      </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1401,45 +1275,45 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
         <v>18</v>
       </c>
       <c r="J13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
         <v>96</v>
-      </c>
-      <c r="K13" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1448,22 +1322,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1475,383 +1349,7 @@
         <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" t="s">
-        <v>109</v>
-      </c>
-      <c r="O15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
-        <v>116</v>
-      </c>
-      <c r="K17" t="s">
-        <v>117</v>
-      </c>
-      <c r="L17" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>120</v>
-      </c>
-      <c r="K18" t="s">
-        <v>121</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" t="s">
-        <v>58</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
-        <v>124</v>
-      </c>
-      <c r="K19" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" t="s">
-        <v>128</v>
-      </c>
-      <c r="K20" t="s">
-        <v>129</v>
-      </c>
-      <c r="L20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" t="s">
-        <v>58</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" t="s">
-        <v>88</v>
-      </c>
-      <c r="L21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" t="s">
-        <v>134</v>
-      </c>
-      <c r="O21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>136</v>
-      </c>
-      <c r="B22" t="s">
-        <v>137</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>138</v>
-      </c>
-      <c r="K22" t="s">
-        <v>139</v>
-      </c>
-      <c r="L22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" t="s">
-        <v>140</v>
-      </c>
-      <c r="O22" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6F13B6C-532F-489E-9068-4AEAE8E651AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E907B3-4BA5-406F-A45F-A1C654EB6DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="134">
   <si>
     <t>Time</t>
   </si>
@@ -203,6 +203,33 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
   </si>
   <si>
+    <t>03/26/2026 1:22:56 PM</t>
+  </si>
+  <si>
+    <t>583</t>
+  </si>
+  <si>
+    <t>Rodney Salcido</t>
+  </si>
+  <si>
+    <t>Construction, Pedestrians, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>I 20, Warfield, TX, 79711</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
+  </si>
+  <si>
     <t>03/22/2026 10:09:28 PM</t>
   </si>
   <si>
@@ -224,12 +251,6 @@
     <t>03/13/2026 9:33:47 AM</t>
   </si>
   <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>Rodney Salcido</t>
-  </si>
-  <si>
     <t>East Interstate 20, 5.4 mi ENE Midland, Midland County, TX, 79702</t>
   </si>
   <si>
@@ -254,12 +275,30 @@
     <t>7606 Tres Hermanas Boulevard, Odessa, TX, 79765</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb1-578c-5827-804c-7990c6190630</t>
   </si>
   <si>
+    <t>03/03/2026 7:19:10 PM</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>Nathan Roe</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Shakespeare Road, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b66d-6c38-58b4-9408-70137dcb76a1</t>
+  </si>
+  <si>
     <t>03/02/2026 3:37:09 PM</t>
   </si>
   <si>
@@ -275,15 +314,39 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b07b-cced-5497-a51f-46c4359728ac</t>
   </si>
   <si>
+    <t>02/27/2026 6:34:29 PM</t>
+  </si>
+  <si>
+    <t>US 87, 26.0 mi NW San Angelo, Sterling County, TX</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a1ab-12c0-5caf-b2f6-baf9d4e12298</t>
+  </si>
+  <si>
+    <t>02/21/2026 3:58:28 PM</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>James Jenkins</t>
+  </si>
+  <si>
+    <t>209 West 8th Street, Odessa, TX, 79763</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458236-1570-5cb7-8371-272bd8f12c91</t>
+  </si>
+  <si>
     <t>02/20/2026 6:02:32 PM</t>
   </si>
   <si>
-    <t>607</t>
-  </si>
-  <si>
-    <t>James Jenkins</t>
-  </si>
-  <si>
     <t>Harsh Turn</t>
   </si>
   <si>
@@ -306,6 +369,45 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457ba8-ebfa-5b43-9827-b1e3862a826a</t>
+  </si>
+  <si>
+    <t>02/13/2026 3:38:17 PM</t>
+  </si>
+  <si>
+    <t>591</t>
+  </si>
+  <si>
+    <t>Interstate Highway 20 Service Road, 17.9 mi WSW Big Spring, Martin County, TX, 79782</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544558f0-bcf4-5e11-83e9-a1959020f984</t>
+  </si>
+  <si>
+    <t>02/12/2026 7:09:16 PM</t>
+  </si>
+  <si>
+    <t>TX 115, 3.2 mi NE Kermit, Winkler County, TX, 79745</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445548b-8833-5d53-90fe-30f4d3a2ec96</t>
+  </si>
+  <si>
+    <t>02/11/2026 5:15:27 PM</t>
+  </si>
+  <si>
+    <t>1740 South Dixie Boulevard, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454efc-fa63-59f7-82ae-fbd6da2d6836</t>
   </si>
   <si>
     <t>02/09/2026 5:58:32 PM</t>
@@ -691,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,10 +1130,10 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1043,19 +1145,19 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1064,21 +1166,21 @@
         <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1090,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1099,10 +1201,10 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>18</v>
@@ -1111,21 +1213,21 @@
         <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1134,7 +1236,7 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
         <v>21</v>
@@ -1158,21 +1260,21 @@
         <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1181,10 +1283,10 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1193,10 +1295,10 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -1208,18 +1310,18 @@
         <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1228,31 +1330,31 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="O12" t="s">
         <v>93</v>
@@ -1263,10 +1365,10 @@
         <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1275,10 +1377,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1287,10 +1389,10 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1302,18 +1404,18 @@
         <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1322,34 +1424,363 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
         <v>21</v>
       </c>
       <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>106</v>
+      </c>
+      <c r="K15" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
         <v>22</v>
       </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" t="s">
+        <v>113</v>
+      </c>
+      <c r="O16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K18" t="s">
+        <v>121</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>124</v>
+      </c>
+      <c r="K19" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
+        <v>128</v>
+      </c>
+      <c r="K20" t="s">
+        <v>129</v>
+      </c>
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
         <v>23</v>
       </c>
-      <c r="K14" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>99</v>
+      <c r="K21" t="s">
+        <v>132</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E907B3-4BA5-406F-A45F-A1C654EB6DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4BB4F28-5BFA-4037-BDCB-272CB118B073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="145">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,64 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>05/01/2026 2:14:13 PM</t>
+    <t>05/09/2026 9:01:35 PM</t>
+  </si>
+  <si>
+    <t>673</t>
+  </si>
+  <si>
+    <t>Colby Smith</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450fd5-44b4-5027-89b3-440a08cb2c22</t>
+  </si>
+  <si>
+    <t>05/09/2026 1:20:47 AM</t>
+  </si>
+  <si>
+    <t>585</t>
+  </si>
+  <si>
+    <t>Nicholas Rodecap</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Slightly Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>County Road 308, 27.7 mi SSE Odessa, Upton County, TX</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b9c-3845-5a7e-82f1-12d91a117dfe</t>
+  </si>
+  <si>
+    <t>05/01/2026 1:14:13 PM</t>
   </si>
   <si>
     <t>516</t>
@@ -71,21 +128,12 @@
     <t>Leonard Ramirez</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Harsh Brake</t>
   </si>
   <si>
     <t>Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>I 20-E Business, Midland, TX, 79712</t>
   </si>
   <si>
@@ -98,7 +146,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e4f6-81e7-5c75-8318-c6dfd58c5b0c</t>
   </si>
   <si>
-    <t>04/07/2026 7:34:13 PM</t>
+    <t>04/07/2026 6:34:13 PM</t>
   </si>
   <si>
     <t>277</t>
@@ -107,9 +155,6 @@
     <t>Hunter McDowell</t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>Passengers, Light Traffic</t>
   </si>
   <si>
@@ -122,7 +167,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
   </si>
   <si>
-    <t>04/02/2026 6:07:12 AM</t>
+    <t>04/02/2026 5:07:12 AM</t>
   </si>
   <si>
     <t>603</t>
@@ -146,7 +191,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
   </si>
   <si>
-    <t>03/29/2026 12:25:48 AM</t>
+    <t>03/28/2026 11:25:48 PM</t>
   </si>
   <si>
     <t>604</t>
@@ -158,16 +203,13 @@
     <t>Rolling Stop</t>
   </si>
   <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
     <t>299 West Ada Street, Odessa, TX, 79761</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445380e-371f-569c-bea6-06003c4f8020</t>
   </si>
   <si>
-    <t>03/27/2026 10:44:31 AM</t>
+    <t>03/27/2026 9:44:31 AM</t>
   </si>
   <si>
     <t>Following Distance</t>
@@ -185,7 +227,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ff7-f025-5aab-90d6-655800596967</t>
   </si>
   <si>
-    <t>03/27/2026 5:29:47 AM</t>
+    <t>03/27/2026 4:29:47 AM</t>
   </si>
   <si>
     <t>Wet Road, Congested, Night</t>
@@ -203,7 +245,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
   </si>
   <si>
-    <t>03/26/2026 1:22:56 PM</t>
+    <t>03/26/2026 12:22:56 PM</t>
   </si>
   <si>
     <t>583</t>
@@ -230,7 +272,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
   </si>
   <si>
-    <t>03/22/2026 10:09:28 PM</t>
+    <t>03/22/2026 9:09:28 PM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic, Night</t>
@@ -248,7 +290,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544518ab-3d01-5bf0-b82b-40d74389918d</t>
   </si>
   <si>
-    <t>03/13/2026 9:33:47 AM</t>
+    <t>03/13/2026 8:33:47 AM</t>
   </si>
   <si>
     <t>East Interstate 20, 5.4 mi ENE Midland, Midland County, TX, 79702</t>
@@ -263,7 +305,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e79e-255b-5dbc-baaf-e9de51a814a8</t>
   </si>
   <si>
-    <t>03/11/2026 11:18:32 AM</t>
+    <t>03/11/2026 10:18:32 AM</t>
   </si>
   <si>
     <t>606</t>
@@ -278,7 +320,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb1-578c-5827-804c-7990c6190630</t>
   </si>
   <si>
-    <t>03/03/2026 7:19:10 PM</t>
+    <t>03/03/2026 6:19:10 PM</t>
   </si>
   <si>
     <t>517</t>
@@ -299,7 +341,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b66d-6c38-58b4-9408-70137dcb76a1</t>
   </si>
   <si>
-    <t>03/02/2026 3:37:09 PM</t>
+    <t>03/02/2026 2:37:09 PM</t>
   </si>
   <si>
     <t>Obstructed Camera</t>
@@ -314,7 +356,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b07b-cced-5497-a51f-46c4359728ac</t>
   </si>
   <si>
-    <t>02/27/2026 6:34:29 PM</t>
+    <t>02/27/2026 5:34:29 PM</t>
   </si>
   <si>
     <t>US 87, 26.0 mi NW San Angelo, Sterling County, TX</t>
@@ -326,7 +368,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a1ab-12c0-5caf-b2f6-baf9d4e12298</t>
   </si>
   <si>
-    <t>02/21/2026 3:58:28 PM</t>
+    <t>02/21/2026 2:58:28 PM</t>
   </si>
   <si>
     <t>607</t>
@@ -344,7 +386,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458236-1570-5cb7-8371-272bd8f12c91</t>
   </si>
   <si>
-    <t>02/20/2026 6:02:32 PM</t>
+    <t>02/20/2026 5:02:32 PM</t>
   </si>
   <si>
     <t>Harsh Turn</t>
@@ -362,7 +404,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457d81-5120-5ae7-9d9e-6c0b590b94e1</t>
   </si>
   <si>
-    <t>02/20/2026 9:26:33 AM</t>
+    <t>02/20/2026 8:26:33 AM</t>
   </si>
   <si>
     <t>West Industrial Avenue, Warfield, TX, 79706</t>
@@ -371,7 +413,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457ba8-ebfa-5b43-9827-b1e3862a826a</t>
   </si>
   <si>
-    <t>02/13/2026 3:38:17 PM</t>
+    <t>02/13/2026 2:38:17 PM</t>
   </si>
   <si>
     <t>591</t>
@@ -386,7 +428,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544558f0-bcf4-5e11-83e9-a1959020f984</t>
   </si>
   <si>
-    <t>02/12/2026 7:09:16 PM</t>
+    <t>02/12/2026 6:09:16 PM</t>
   </si>
   <si>
     <t>TX 115, 3.2 mi NE Kermit, Winkler County, TX, 79745</t>
@@ -398,7 +440,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445548b-8833-5d53-90fe-30f4d3a2ec96</t>
   </si>
   <si>
-    <t>02/11/2026 5:15:27 PM</t>
+    <t>02/11/2026 4:15:27 PM</t>
   </si>
   <si>
     <t>1740 South Dixie Boulevard, Odessa, TX, 79761</t>
@@ -408,15 +450,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454efc-fa63-59f7-82ae-fbd6da2d6836</t>
-  </si>
-  <si>
-    <t>02/09/2026 5:58:32 PM</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544544d7-b107-5005-9aaa-fbe04e586345</t>
   </si>
 </sst>
 </file>
@@ -793,10 +826,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -843,7 +876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -884,33 +917,33 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
       </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -919,42 +952,42 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" t="s">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
@@ -984,7 +1017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -1001,10 +1034,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
         <v>46</v>
-      </c>
-      <c r="G5" t="s">
-        <v>47</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1013,10 +1046,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
         <v>48</v>
-      </c>
-      <c r="K5" t="s">
-        <v>40</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1031,15 +1064,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1048,10 +1081,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1060,10 +1093,10 @@
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1072,21 +1105,21 @@
         <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="O6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1095,10 +1128,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1107,34 +1140,34 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
         <v>59</v>
       </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="C8" t="s">
         <v>60</v>
       </c>
-      <c r="O7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
       <c r="D8" t="s">
         <v>18</v>
       </c>
@@ -1142,13 +1175,13 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
@@ -1166,33 +1199,33 @@
         <v>18</v>
       </c>
       <c r="N8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
         <v>69</v>
       </c>
-      <c r="O8" t="s">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
         <v>71</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1201,33 +1234,33 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" t="s">
         <v>73</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
         <v>74</v>
       </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>75</v>
       </c>
-      <c r="O9" t="s">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1236,22 +1269,22 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s">
         <v>18</v>
@@ -1260,21 +1293,21 @@
         <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1283,10 +1316,10 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1295,10 +1328,10 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -1307,21 +1340,21 @@
         <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1330,45 +1363,45 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1377,10 +1410,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1389,292 +1422,292 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K13" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" t="s">
         <v>97</v>
       </c>
-      <c r="L13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="C16" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>40</v>
+      </c>
+      <c r="N16" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>120</v>
+      </c>
+      <c r="K17" t="s">
+        <v>121</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" t="s">
         <v>66</v>
       </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>100</v>
-      </c>
-      <c r="K14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>106</v>
-      </c>
-      <c r="K15" t="s">
-        <v>107</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="H18" t="s">
         <v>22</v>
       </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" t="s">
-        <v>111</v>
-      </c>
-      <c r="K16" t="s">
-        <v>112</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" t="s">
-        <v>113</v>
-      </c>
-      <c r="O16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
         <v>22</v>
       </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
-        <v>116</v>
-      </c>
-      <c r="K17" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>120</v>
-      </c>
-      <c r="K18" t="s">
-        <v>121</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" t="s">
-        <v>66</v>
-      </c>
       <c r="I19" t="s">
         <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K19" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -1686,18 +1719,18 @@
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1706,22 +1739,22 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s">
         <v>18</v>
@@ -1733,18 +1766,18 @@
         <v>18</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -1753,22 +1786,22 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
         <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="K21" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="L21" t="s">
         <v>18</v>
@@ -1780,7 +1813,54 @@
         <v>18</v>
       </c>
       <c r="O21" t="s">
-        <v>133</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>142</v>
+      </c>
+      <c r="K22" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4BB4F28-5BFA-4037-BDCB-272CB118B073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD877445-89C4-434A-BA5D-2DA5520B4932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Time</t>
   </si>
@@ -411,45 +411,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457ba8-ebfa-5b43-9827-b1e3862a826a</t>
-  </si>
-  <si>
-    <t>02/13/2026 2:38:17 PM</t>
-  </si>
-  <si>
-    <t>591</t>
-  </si>
-  <si>
-    <t>Interstate Highway 20 Service Road, 17.9 mi WSW Big Spring, Martin County, TX, 79782</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544558f0-bcf4-5e11-83e9-a1959020f984</t>
-  </si>
-  <si>
-    <t>02/12/2026 6:09:16 PM</t>
-  </si>
-  <si>
-    <t>TX 115, 3.2 mi NE Kermit, Winkler County, TX, 79745</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445548b-8833-5d53-90fe-30f4d3a2ec96</t>
-  </si>
-  <si>
-    <t>02/11/2026 4:15:27 PM</t>
-  </si>
-  <si>
-    <t>1740 South Dixie Boulevard, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454efc-fa63-59f7-82ae-fbd6da2d6836</t>
   </si>
 </sst>
 </file>
@@ -826,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1722,147 +1683,6 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" t="s">
-        <v>134</v>
-      </c>
-      <c r="K20" t="s">
-        <v>135</v>
-      </c>
-      <c r="L20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s">
-        <v>138</v>
-      </c>
-      <c r="K21" t="s">
-        <v>139</v>
-      </c>
-      <c r="L21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" t="s">
-        <v>80</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>142</v>
-      </c>
-      <c r="K22" t="s">
-        <v>143</v>
-      </c>
-      <c r="L22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" t="s">
-        <v>144</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD877445-89C4-434A-BA5D-2DA5520B4932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D04708-FC42-4ED3-8124-9E1C02DC8177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="127">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,67 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>05/09/2026 9:01:35 PM</t>
+    <t>05/21/2026 11:45:40 AM</t>
+  </si>
+  <si>
+    <t>583</t>
+  </si>
+  <si>
+    <t>Rodney Salcido</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>200 East Interstate 20, Odessa, TX, 79766</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b6d-b10b-568b-ae54-23edd2e56ee2</t>
+  </si>
+  <si>
+    <t>05/18/2026 3:55:26 PM</t>
+  </si>
+  <si>
+    <t>672</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>11610 West Interstate 20, Warfield, TX, 79706</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453cdf-486f-5a10-b9ac-9478e42505a0</t>
+  </si>
+  <si>
+    <t>05/09/2026 10:01:35 PM</t>
   </si>
   <si>
     <t>673</t>
@@ -71,21 +131,12 @@
     <t>Colby Smith</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
   </si>
   <si>
@@ -95,7 +146,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450fd5-44b4-5027-89b3-440a08cb2c22</t>
   </si>
   <si>
-    <t>05/09/2026 1:20:47 AM</t>
+    <t>05/09/2026 2:20:47 AM</t>
   </si>
   <si>
     <t>585</t>
@@ -119,7 +170,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b9c-3845-5a7e-82f1-12d91a117dfe</t>
   </si>
   <si>
-    <t>05/01/2026 1:14:13 PM</t>
+    <t>05/01/2026 2:14:13 PM</t>
   </si>
   <si>
     <t>516</t>
@@ -128,12 +179,6 @@
     <t>Leonard Ramirez</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>I 20-E Business, Midland, TX, 79712</t>
   </si>
   <si>
@@ -146,7 +191,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e4f6-81e7-5c75-8318-c6dfd58c5b0c</t>
   </si>
   <si>
-    <t>04/07/2026 6:34:13 PM</t>
+    <t>04/07/2026 7:34:13 PM</t>
   </si>
   <si>
     <t>277</t>
@@ -167,7 +212,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
   </si>
   <si>
-    <t>04/02/2026 5:07:12 AM</t>
+    <t>04/02/2026 6:07:12 AM</t>
   </si>
   <si>
     <t>603</t>
@@ -191,7 +236,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
   </si>
   <si>
-    <t>03/28/2026 11:25:48 PM</t>
+    <t>03/29/2026 12:25:48 AM</t>
   </si>
   <si>
     <t>604</t>
@@ -209,10 +254,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445380e-371f-569c-bea6-06003c4f8020</t>
   </si>
   <si>
-    <t>03/27/2026 9:44:31 AM</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
+    <t>03/27/2026 10:44:31 AM</t>
   </si>
   <si>
     <t>Moderate Traffic</t>
@@ -227,7 +269,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ff7-f025-5aab-90d6-655800596967</t>
   </si>
   <si>
-    <t>03/27/2026 4:29:47 AM</t>
+    <t>03/27/2026 5:29:47 AM</t>
   </si>
   <si>
     <t>Wet Road, Congested, Night</t>
@@ -245,34 +287,22 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
   </si>
   <si>
-    <t>03/26/2026 12:22:56 PM</t>
-  </si>
-  <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>Rodney Salcido</t>
+    <t>03/26/2026 1:22:56 PM</t>
   </si>
   <si>
     <t>Construction, Pedestrians, Moderate Traffic</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>I 20, Warfield, TX, 79711</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>0.51</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
   </si>
   <si>
-    <t>03/22/2026 9:09:28 PM</t>
+    <t>03/22/2026 10:09:28 PM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic, Night</t>
@@ -290,7 +320,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544518ab-3d01-5bf0-b82b-40d74389918d</t>
   </si>
   <si>
-    <t>03/13/2026 8:33:47 AM</t>
+    <t>03/13/2026 9:33:47 AM</t>
   </si>
   <si>
     <t>East Interstate 20, 5.4 mi ENE Midland, Midland County, TX, 79702</t>
@@ -305,7 +335,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e79e-255b-5dbc-baaf-e9de51a814a8</t>
   </si>
   <si>
-    <t>03/11/2026 10:18:32 AM</t>
+    <t>03/11/2026 11:18:32 AM</t>
   </si>
   <si>
     <t>606</t>
@@ -320,7 +350,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb1-578c-5827-804c-7990c6190630</t>
   </si>
   <si>
-    <t>03/03/2026 6:19:10 PM</t>
+    <t>03/03/2026 7:19:10 PM</t>
   </si>
   <si>
     <t>517</t>
@@ -341,7 +371,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b66d-6c38-58b4-9408-70137dcb76a1</t>
   </si>
   <si>
-    <t>03/02/2026 2:37:09 PM</t>
+    <t>03/02/2026 3:37:09 PM</t>
   </si>
   <si>
     <t>Obstructed Camera</t>
@@ -356,7 +386,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b07b-cced-5497-a51f-46c4359728ac</t>
   </si>
   <si>
-    <t>02/27/2026 5:34:29 PM</t>
+    <t>02/27/2026 6:34:29 PM</t>
   </si>
   <si>
     <t>US 87, 26.0 mi NW San Angelo, Sterling County, TX</t>
@@ -366,51 +396,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a1ab-12c0-5caf-b2f6-baf9d4e12298</t>
-  </si>
-  <si>
-    <t>02/21/2026 2:58:28 PM</t>
-  </si>
-  <si>
-    <t>607</t>
-  </si>
-  <si>
-    <t>James Jenkins</t>
-  </si>
-  <si>
-    <t>209 West 8th Street, Odessa, TX, 79763</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458236-1570-5cb7-8371-272bd8f12c91</t>
-  </si>
-  <si>
-    <t>02/20/2026 5:02:32 PM</t>
-  </si>
-  <si>
-    <t>Harsh Turn</t>
-  </si>
-  <si>
-    <t>6101 Highway 80, Odessa, TX, 79762</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457d81-5120-5ae7-9d9e-6c0b590b94e1</t>
-  </si>
-  <si>
-    <t>02/20/2026 8:26:33 AM</t>
-  </si>
-  <si>
-    <t>West Industrial Avenue, Warfield, TX, 79706</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457ba8-ebfa-5b43-9827-b1e3862a826a</t>
   </si>
 </sst>
 </file>
@@ -787,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -878,21 +863,21 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -907,16 +892,16 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -928,18 +913,18 @@
         <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -948,10 +933,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -960,10 +945,10 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -972,7 +957,7 @@
         <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
@@ -995,10 +980,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1007,10 +992,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1022,18 +1007,18 @@
         <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1042,10 +1027,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1089,10 +1074,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
         <v>61</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1104,7 +1089,7 @@
         <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1116,18 +1101,18 @@
         <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1136,10 +1121,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1148,10 +1133,10 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1160,21 +1145,21 @@
         <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1183,10 +1168,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1195,10 +1180,10 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
         <v>18</v>
@@ -1207,21 +1192,21 @@
         <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1230,13 +1215,13 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
         <v>18</v>
@@ -1254,21 +1239,21 @@
         <v>18</v>
       </c>
       <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
         <v>83</v>
-      </c>
-      <c r="O10" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1277,10 +1262,10 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1289,33 +1274,33 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" t="s">
         <v>87</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
         <v>88</v>
       </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>89</v>
-      </c>
-      <c r="O11" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1324,13 +1309,13 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
@@ -1348,21 +1333,21 @@
         <v>18</v>
       </c>
       <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" t="s">
         <v>94</v>
-      </c>
-      <c r="O12" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1371,10 +1356,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1383,19 +1368,19 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
         <v>99</v>
-      </c>
-      <c r="K13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" t="s">
-        <v>18</v>
       </c>
       <c r="O13" t="s">
         <v>100</v>
@@ -1406,10 +1391,10 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1418,45 +1403,45 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" t="s">
         <v>104</v>
       </c>
-      <c r="G14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="O14" t="s">
         <v>105</v>
-      </c>
-      <c r="K14" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" t="s">
-        <v>40</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
         <v>108</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1465,10 +1450,10 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1477,33 +1462,33 @@
         <v>18</v>
       </c>
       <c r="J15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" t="s">
         <v>110</v>
-      </c>
-      <c r="K15" t="s">
-        <v>111</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
         <v>113</v>
-      </c>
-      <c r="B16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1512,45 +1497,45 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N16" t="s">
         <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1559,13 +1544,13 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
         <v>18</v>
@@ -1594,10 +1579,10 @@
         <v>123</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1606,81 +1591,34 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
         <v>124</v>
       </c>
-      <c r="G18" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>125</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" t="s">
         <v>126</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
-        <v>127</v>
-      </c>
-      <c r="O18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
-        <v>130</v>
-      </c>
-      <c r="K19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D04708-FC42-4ED3-8124-9E1C02DC8177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE4A6503-2EDC-4146-AD3A-890EEADBEB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="119">
   <si>
     <t>Time</t>
   </si>
@@ -62,243 +62,231 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>05/21/2026 11:45:40 AM</t>
+    <t>05/18/2026 3:55:26 PM</t>
+  </si>
+  <si>
+    <t>672</t>
+  </si>
+  <si>
+    <t>Rodney Salcido</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>11610 West Interstate 20, Warfield, TX, 79706</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453cdf-486f-5a10-b9ac-9478e42505a0</t>
+  </si>
+  <si>
+    <t>05/09/2026 10:01:35 PM</t>
+  </si>
+  <si>
+    <t>673</t>
+  </si>
+  <si>
+    <t>Colby Smith</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450fd5-44b4-5027-89b3-440a08cb2c22</t>
+  </si>
+  <si>
+    <t>05/09/2026 2:20:47 AM</t>
+  </si>
+  <si>
+    <t>585</t>
+  </si>
+  <si>
+    <t>Nicholas Rodecap</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Slightly Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>County Road 308, 27.7 mi SSE Odessa, Upton County, TX</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b9c-3845-5a7e-82f1-12d91a117dfe</t>
+  </si>
+  <si>
+    <t>05/01/2026 2:14:13 PM</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Leonard Ramirez</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>I 20-E Business, Midland, TX, 79712</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e4f6-81e7-5c75-8318-c6dfd58c5b0c</t>
+  </si>
+  <si>
+    <t>04/07/2026 7:34:13 PM</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Hunter McDowell</t>
+  </si>
+  <si>
+    <t>Passengers, Light Traffic</t>
+  </si>
+  <si>
+    <t>3175 Tanglewood Lane, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
+  </si>
+  <si>
+    <t>04/02/2026 6:07:12 AM</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Larry Richardson</t>
+  </si>
+  <si>
+    <t>Wet Road, Moderate Traffic, Night</t>
+  </si>
+  <si>
+    <t>South Grant Avenue, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
+  </si>
+  <si>
+    <t>03/29/2026 12:25:48 AM</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Colby Miller</t>
+  </si>
+  <si>
+    <t>Rolling Stop</t>
+  </si>
+  <si>
+    <t>299 West Ada Street, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445380e-371f-569c-bea6-06003c4f8020</t>
+  </si>
+  <si>
+    <t>03/27/2026 10:44:31 AM</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>2000 South FM 1788, Midland, TX, 79711</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ff7-f025-5aab-90d6-655800596967</t>
+  </si>
+  <si>
+    <t>03/27/2026 5:29:47 AM</t>
+  </si>
+  <si>
+    <t>Wet Road, Congested, Night</t>
+  </si>
+  <si>
+    <t>103 West 42nd Street (Chris Kyle Memorial Highway), Odessa, TX, 79764</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
+  </si>
+  <si>
+    <t>03/26/2026 1:22:56 PM</t>
   </si>
   <si>
     <t>583</t>
   </si>
   <si>
-    <t>Rodney Salcido</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>200 East Interstate 20, Odessa, TX, 79766</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>Construction, Pedestrians, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Warfield, TX, 79711</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>0.51</t>
   </si>
   <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b6d-b10b-568b-ae54-23edd2e56ee2</t>
-  </si>
-  <si>
-    <t>05/18/2026 3:55:26 PM</t>
-  </si>
-  <si>
-    <t>672</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>11610 West Interstate 20, Warfield, TX, 79706</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453cdf-486f-5a10-b9ac-9478e42505a0</t>
-  </si>
-  <si>
-    <t>05/09/2026 10:01:35 PM</t>
-  </si>
-  <si>
-    <t>673</t>
-  </si>
-  <si>
-    <t>Colby Smith</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450fd5-44b4-5027-89b3-440a08cb2c22</t>
-  </si>
-  <si>
-    <t>05/09/2026 2:20:47 AM</t>
-  </si>
-  <si>
-    <t>585</t>
-  </si>
-  <si>
-    <t>Nicholas Rodecap</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
-    <t>Slightly Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>County Road 308, 27.7 mi SSE Odessa, Upton County, TX</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b9c-3845-5a7e-82f1-12d91a117dfe</t>
-  </si>
-  <si>
-    <t>05/01/2026 2:14:13 PM</t>
-  </si>
-  <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Leonard Ramirez</t>
-  </si>
-  <si>
-    <t>I 20-E Business, Midland, TX, 79712</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e4f6-81e7-5c75-8318-c6dfd58c5b0c</t>
-  </si>
-  <si>
-    <t>04/07/2026 7:34:13 PM</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Hunter McDowell</t>
-  </si>
-  <si>
-    <t>Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>3175 Tanglewood Lane, Odessa, TX, 79762</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
-  </si>
-  <si>
-    <t>04/02/2026 6:07:12 AM</t>
-  </si>
-  <si>
-    <t>603</t>
-  </si>
-  <si>
-    <t>Larry Richardson</t>
-  </si>
-  <si>
-    <t>Wet Road, Moderate Traffic, Night</t>
-  </si>
-  <si>
-    <t>South Grant Avenue, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
-  </si>
-  <si>
-    <t>03/29/2026 12:25:48 AM</t>
-  </si>
-  <si>
-    <t>604</t>
-  </si>
-  <si>
-    <t>Colby Miller</t>
-  </si>
-  <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
-    <t>299 West Ada Street, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445380e-371f-569c-bea6-06003c4f8020</t>
-  </si>
-  <si>
-    <t>03/27/2026 10:44:31 AM</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>2000 South FM 1788, Midland, TX, 79711</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ff7-f025-5aab-90d6-655800596967</t>
-  </si>
-  <si>
-    <t>03/27/2026 5:29:47 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Congested, Night</t>
-  </si>
-  <si>
-    <t>103 West 42nd Street (Chris Kyle Memorial Highway), Odessa, TX, 79764</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
-  </si>
-  <si>
-    <t>03/26/2026 1:22:56 PM</t>
-  </si>
-  <si>
-    <t>Construction, Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>I 20, Warfield, TX, 79711</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
   </si>
   <si>
@@ -384,18 +372,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b07b-cced-5497-a51f-46c4359728ac</t>
-  </si>
-  <si>
-    <t>02/27/2026 6:34:29 PM</t>
-  </si>
-  <si>
-    <t>US 87, 26.0 mi NW San Angelo, Sterling County, TX</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a1ab-12c0-5caf-b2f6-baf9d4e12298</t>
   </si>
 </sst>
 </file>
@@ -772,10 +748,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -822,7 +798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -863,21 +839,21 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
       </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -916,7 +892,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -939,7 +915,7 @@
         <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -963,7 +939,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -986,7 +962,7 @@
         <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1004,21 +980,21 @@
         <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1027,22 +1003,22 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1051,21 +1027,21 @@
         <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1074,22 +1050,22 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1098,21 +1074,21 @@
         <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="O7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1121,22 +1097,22 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1145,21 +1121,21 @@
         <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1168,45 +1144,45 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" t="s">
         <v>76</v>
       </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
         <v>77</v>
       </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>79</v>
-      </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1215,45 +1191,45 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
         <v>80</v>
       </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>81</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
         <v>82</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
       </c>
       <c r="O10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1262,10 +1238,10 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1274,10 +1250,10 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -1286,21 +1262,21 @@
         <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1309,10 +1285,10 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
@@ -1321,10 +1297,10 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
@@ -1333,21 +1309,21 @@
         <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="O12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1356,22 +1332,22 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I13" t="s">
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1380,21 +1356,21 @@
         <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1403,22 +1379,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1427,21 +1403,21 @@
         <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1450,10 +1426,10 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1462,33 +1438,33 @@
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K15" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="N15" t="s">
         <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1497,10 +1473,10 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
         <v>31</v>
@@ -1509,116 +1485,22 @@
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="N16" t="s">
         <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
         <v>118</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
-        <v>120</v>
-      </c>
-      <c r="K17" t="s">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K18" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE4A6503-2EDC-4146-AD3A-890EEADBEB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97DB8DC6-BB9A-4646-9B2C-592CF31B4991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Time</t>
   </si>
@@ -62,27 +62,132 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/03/2026 1:17:18 PM</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>Nathan Roe</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Northwest Loop 338, Westside, TX, 79767</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458eb4-436d-5442-b353-f930bce641f0</t>
+  </si>
+  <si>
+    <t>06/02/2026 3:36:18 PM</t>
+  </si>
+  <si>
+    <t>583</t>
+  </si>
+  <si>
+    <t>Rodney Salcido</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Odessa, TX, 79760</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458a0d-2877-5170-a4a3-3dc86ca45e81</t>
+  </si>
+  <si>
+    <t>06/02/2026 3:17:57 PM</t>
+  </si>
+  <si>
+    <t>South Grandview Avenue, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544589fc-5cea-50cb-8128-35cb402cd18d</t>
+  </si>
+  <si>
+    <t>05/29/2026 12:01:35 PM</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Leonard Ramirez</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic</t>
+  </si>
+  <si>
+    <t>North Grandview Avenue, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574af-244b-51d9-936e-a9522a16ec6e</t>
+  </si>
+  <si>
+    <t>05/29/2026 8:13:59 AM</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Hunter McDowell</t>
+  </si>
+  <si>
+    <t>Forward Collision Warning</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>East 2nd Street, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544573de-c59e-58a0-85bc-46a91e8c6b76</t>
+  </si>
+  <si>
     <t>05/18/2026 3:55:26 PM</t>
   </si>
   <si>
     <t>672</t>
   </si>
   <si>
-    <t>Rodney Salcido</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Following Distance</t>
   </si>
   <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
     <t>Coached</t>
   </si>
   <si>
@@ -110,9 +215,6 @@
     <t>Light Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
   </si>
   <si>
@@ -149,15 +251,6 @@
     <t>05/01/2026 2:14:13 PM</t>
   </si>
   <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Leonard Ramirez</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Light Traffic</t>
   </si>
   <si>
@@ -176,12 +269,6 @@
     <t>04/07/2026 7:34:13 PM</t>
   </si>
   <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Hunter McDowell</t>
-  </si>
-  <si>
     <t>Passengers, Light Traffic</t>
   </si>
   <si>
@@ -212,9 +299,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>0.57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
   </si>
   <si>
@@ -239,9 +323,6 @@
     <t>03/27/2026 10:44:31 AM</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>2000 South FM 1788, Midland, TX, 79711</t>
   </si>
   <si>
@@ -272,9 +353,6 @@
     <t>03/26/2026 1:22:56 PM</t>
   </si>
   <si>
-    <t>583</t>
-  </si>
-  <si>
     <t>Construction, Pedestrians, Moderate Traffic</t>
   </si>
   <si>
@@ -317,9 +395,6 @@
     <t>40</t>
   </si>
   <si>
-    <t>0.64</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e79e-255b-5dbc-baaf-e9de51a814a8</t>
   </si>
   <si>
@@ -336,42 +411,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb1-578c-5827-804c-7990c6190630</t>
-  </si>
-  <si>
-    <t>03/03/2026 7:19:10 PM</t>
-  </si>
-  <si>
-    <t>517</t>
-  </si>
-  <si>
-    <t>Nathan Roe</t>
-  </si>
-  <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
-    <t>Shakespeare Road, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b66d-6c38-58b4-9408-70137dcb76a1</t>
-  </si>
-  <si>
-    <t>03/02/2026 3:37:09 PM</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
-    <t>US 385, 8.5 mi SSE Andrews, Andrews County, TX, 79714</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b07b-cced-5497-a51f-46c4359728ac</t>
   </si>
 </sst>
 </file>
@@ -748,10 +787,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -798,7 +837,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -818,689 +857,830 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" t="s">
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" t="s">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
+      <c r="K4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="K4" t="s">
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
         <v>41</v>
       </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="K5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" t="s">
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
+      <c r="O5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>46</v>
       </c>
-      <c r="G5" t="s">
+      <c r="B6" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="C6" t="s">
         <v>48</v>
       </c>
-      <c r="K5" t="s">
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>49</v>
       </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="O5" t="s">
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="K6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" t="s">
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" t="s">
         <v>53</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="H7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
+      <c r="O12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
         <v>56</v>
       </c>
-      <c r="K6" t="s">
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>109</v>
+      </c>
+      <c r="O15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" t="s">
         <v>57</v>
       </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>113</v>
+      </c>
+      <c r="K16" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" t="s">
+        <v>115</v>
+      </c>
+      <c r="O16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>119</v>
+      </c>
+      <c r="K17" t="s">
+        <v>120</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>121</v>
+      </c>
+      <c r="O17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
         <v>78</v>
       </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>82</v>
-      </c>
-      <c r="O10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
-        <v>89</v>
-      </c>
-      <c r="O11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" t="s">
-        <v>93</v>
-      </c>
-      <c r="K12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" t="s">
-        <v>95</v>
-      </c>
-      <c r="O12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>124</v>
+      </c>
+      <c r="K18" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
         <v>98</v>
       </c>
-      <c r="K13" t="s">
-        <v>99</v>
-      </c>
-      <c r="L13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" t="s">
-        <v>100</v>
-      </c>
-      <c r="O13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" t="s">
-        <v>112</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>49</v>
-      </c>
-      <c r="N15" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="G19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>130</v>
+      </c>
+      <c r="K19" t="s">
         <v>114</v>
       </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>115</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" t="s">
-        <v>116</v>
-      </c>
-      <c r="K16" t="s">
-        <v>117</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" t="s">
-        <v>118</v>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97DB8DC6-BB9A-4646-9B2C-592CF31B4991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DA9A439-6DA8-4092-A9AF-F098113387A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="135">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,84 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/08/2026 7:17:58 PM</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Leonard Ramirez</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>I 20, Penwell, TX</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a9be-42c9-5b4d-940e-aa0d0bc99ce7</t>
+  </si>
+  <si>
+    <t>06/07/2026 10:08:28 PM</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Larry Richardson</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>West 13th Street, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a533-ff4c-569f-b5ff-375990f785e7</t>
+  </si>
+  <si>
+    <t>06/05/2026 8:46:40 AM</t>
+  </si>
+  <si>
+    <t>583</t>
+  </si>
+  <si>
+    <t>Rodney Salcido</t>
+  </si>
+  <si>
+    <t>FM 181, JY Ranch, TX</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459809-35c1-59bb-a9f3-05aab0fdce0a</t>
+  </si>
+  <si>
     <t>06/03/2026 1:17:18 PM</t>
   </si>
   <si>
@@ -71,18 +149,9 @@
     <t>Nathan Roe</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Obstructed Camera</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>Northwest Loop 338, Westside, TX, 79767</t>
   </si>
   <si>
@@ -95,15 +164,6 @@
     <t>06/02/2026 3:36:18 PM</t>
   </si>
   <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>Rodney Salcido</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Construction, Light Traffic</t>
   </si>
   <si>
@@ -134,12 +194,6 @@
     <t>05/29/2026 12:01:35 PM</t>
   </si>
   <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Leonard Ramirez</t>
-  </si>
-  <si>
     <t>Wet Road, Light Traffic</t>
   </si>
   <si>
@@ -185,9 +239,6 @@
     <t>672</t>
   </si>
   <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
     <t>Coached</t>
   </si>
   <si>
@@ -212,9 +263,6 @@
     <t>Mobile Usage</t>
   </si>
   <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
     <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
   </si>
   <si>
@@ -251,15 +299,9 @@
     <t>05/01/2026 2:14:13 PM</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>I 20-E Business, Midland, TX, 79712</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>0.58</t>
   </si>
   <si>
@@ -284,12 +326,6 @@
     <t>04/02/2026 6:07:12 AM</t>
   </si>
   <si>
-    <t>603</t>
-  </si>
-  <si>
-    <t>Larry Richardson</t>
-  </si>
-  <si>
     <t>Wet Road, Moderate Traffic, Night</t>
   </si>
   <si>
@@ -384,33 +420,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544518ab-3d01-5bf0-b82b-40d74389918d</t>
-  </si>
-  <si>
-    <t>03/13/2026 9:33:47 AM</t>
-  </si>
-  <si>
-    <t>East Interstate 20, 5.4 mi ENE Midland, Midland County, TX, 79702</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e79e-255b-5dbc-baaf-e9de51a814a8</t>
-  </si>
-  <si>
-    <t>03/11/2026 11:18:32 AM</t>
-  </si>
-  <si>
-    <t>606</t>
-  </si>
-  <si>
-    <t>Fabian Velasco</t>
-  </si>
-  <si>
-    <t>7606 Tres Hermanas Boulevard, Odessa, TX, 79765</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb1-578c-5827-804c-7990c6190630</t>
   </si>
 </sst>
 </file>
@@ -787,10 +796,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -837,7 +846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -857,66 +866,66 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -925,21 +934,21 @@
         <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -951,90 +960,90 @@
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
@@ -1042,645 +1051,692 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
         <v>49</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>51</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
         <v>52</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
       </c>
       <c r="O6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
       <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="s">
+      <c r="K7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
         <v>29</v>
       </c>
-      <c r="H7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="G15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
         <v>62</v>
       </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="O15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" t="s">
+        <v>120</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" t="s">
+        <v>121</v>
+      </c>
+      <c r="O18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" t="s">
         <v>74</v>
       </c>
-      <c r="K9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" t="s">
-        <v>80</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>81</v>
-      </c>
-      <c r="O10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>85</v>
-      </c>
-      <c r="K11" t="s">
-        <v>86</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" t="s">
-        <v>93</v>
-      </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" t="s">
-        <v>44</v>
-      </c>
-      <c r="O12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" t="s">
-        <v>93</v>
-      </c>
-      <c r="L13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>102</v>
-      </c>
-      <c r="K14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" t="s">
-        <v>109</v>
-      </c>
-      <c r="O15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" t="s">
-        <v>112</v>
-      </c>
-      <c r="H16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" t="s">
-        <v>113</v>
-      </c>
-      <c r="K16" t="s">
-        <v>114</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" t="s">
-        <v>115</v>
-      </c>
-      <c r="O16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
-        <v>119</v>
-      </c>
-      <c r="K17" t="s">
-        <v>120</v>
-      </c>
-      <c r="L17" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" t="s">
-        <v>121</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
         <v>125</v>
       </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="K19" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
         <v>127</v>
       </c>
-      <c r="B19" t="s">
+      <c r="O19" t="s">
         <v>128</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>129</v>
       </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
         <v>130</v>
       </c>
-      <c r="K19" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
         <v>131</v>
+      </c>
+      <c r="K20" t="s">
+        <v>132</v>
+      </c>
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
+        <v>133</v>
+      </c>
+      <c r="O20" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DA9A439-6DA8-4092-A9AF-F098113387A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8AF51CC-3FEC-4729-B862-0349BC56BC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="151">
   <si>
     <t>Time</t>
   </si>
@@ -62,30 +62,120 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/18/2026 7:16:38 PM</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Leonard Ramirez</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>East 2nd Street, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd3c-9fc7-5cc9-9733-6ab33059920f</t>
+  </si>
+  <si>
+    <t>06/17/2026 11:00:09 AM</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>I 20;TX 158, Midland, TX, 79706</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d64f-baab-561e-9e3f-7ec3d8e646be</t>
+  </si>
+  <si>
+    <t>06/16/2026 3:47:27 AM</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Colby Miller</t>
+  </si>
+  <si>
+    <t>Harsh Turn</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>East Highway 80, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cf9d-382b-5dbe-b1df-13b8573088b3</t>
+  </si>
+  <si>
+    <t>06/15/2026 2:31:48 PM</t>
+  </si>
+  <si>
+    <t>FM 181, 17.6 mi SW Seminole, Gaines County, TX</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ccc4-c870-5d84-9a44-42750cb7b81f</t>
+  </si>
+  <si>
+    <t>06/12/2026 9:30:43 AM</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Construction, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>FM 181, 14.6 mi WSW Andrews, Andrews County, TX</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3e-0c9c-5ba1-937d-ac0319ff2062</t>
+  </si>
+  <si>
     <t>06/08/2026 7:17:58 PM</t>
   </si>
   <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Leonard Ramirez</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Following Distance</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>I 20, Penwell, TX</t>
   </si>
   <si>
@@ -104,12 +194,6 @@
     <t>Larry Richardson</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
     <t>West 13th Street, Odessa, TX, 79761</t>
   </si>
   <si>
@@ -131,6 +215,9 @@
     <t>Rodney Salcido</t>
   </si>
   <si>
+    <t>Coached</t>
+  </si>
+  <si>
     <t>FM 181, JY Ranch, TX</t>
   </si>
   <si>
@@ -149,9 +236,6 @@
     <t>Nathan Roe</t>
   </si>
   <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
     <t>Northwest Loop 338, Westside, TX, 79767</t>
   </si>
   <si>
@@ -224,9 +308,6 @@
     <t>Moderate Traffic</t>
   </si>
   <si>
-    <t>East 2nd Street, Odessa, TX, 79761</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -239,9 +320,6 @@
     <t>672</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>11610 West Interstate 20, Warfield, TX, 79706</t>
   </si>
   <si>
@@ -260,9 +338,6 @@
     <t>Colby Smith</t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>TX 302, 3.8 mi WNW Odessa, Ector County, TX, 79764</t>
   </si>
   <si>
@@ -341,12 +416,6 @@
     <t>03/29/2026 12:25:48 AM</t>
   </si>
   <si>
-    <t>604</t>
-  </si>
-  <si>
-    <t>Colby Miller</t>
-  </si>
-  <si>
     <t>Rolling Stop</t>
   </si>
   <si>
@@ -380,9 +449,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>0.65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
   </si>
   <si>
@@ -402,24 +468,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
-  </si>
-  <si>
-    <t>03/22/2026 10:09:28 PM</t>
-  </si>
-  <si>
-    <t>Wet Road, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>4305 North Grandview Avenue, Odessa, TX, 79762</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544518ab-3d01-5bf0-b82b-40d74389918d</t>
   </si>
 </sst>
 </file>
@@ -796,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -898,22 +946,22 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -922,10 +970,10 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -934,33 +982,33 @@
         <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
         <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -969,33 +1017,33 @@
         <v>18</v>
       </c>
       <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
         <v>38</v>
       </c>
-      <c r="K4" t="s">
+      <c r="O4" t="s">
         <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -1004,10 +1052,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1016,10 +1064,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1031,18 +1079,18 @@
         <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1051,10 +1099,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1063,33 +1111,33 @@
         <v>18</v>
       </c>
       <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" t="s">
         <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" t="s">
-        <v>52</v>
-      </c>
-      <c r="O6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1098,10 +1146,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1110,34 +1158,34 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
         <v>55</v>
-      </c>
-      <c r="K7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
         <v>58</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" t="s">
         <v>18</v>
       </c>
@@ -1145,10 +1193,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1157,174 +1205,174 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" t="s">
         <v>60</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
         <v>61</v>
       </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>62</v>
-      </c>
-      <c r="O8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
         <v>64</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
         <v>66</v>
       </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
         <v>67</v>
       </c>
-      <c r="G9" t="s">
+      <c r="K9" t="s">
         <v>68</v>
       </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
         <v>69</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
         <v>72</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
         <v>73</v>
       </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
         <v>74</v>
       </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
         <v>75</v>
-      </c>
-      <c r="K10" t="s">
-        <v>76</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
         <v>78</v>
       </c>
-      <c r="B11" t="s">
+      <c r="K11" t="s">
         <v>79</v>
       </c>
-      <c r="C11" t="s">
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
         <v>80</v>
       </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="O11" t="s">
         <v>81</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>82</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1333,10 +1381,10 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -1345,10 +1393,10 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
@@ -1360,12 +1408,12 @@
         <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1380,10 +1428,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1392,10 +1440,10 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1404,21 +1452,21 @@
         <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1427,10 +1475,10 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -1439,10 +1487,10 @@
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="K14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1454,65 +1502,65 @@
         <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" t="s">
         <v>102</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" t="s">
         <v>103</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>104</v>
-      </c>
-      <c r="K15" t="s">
-        <v>105</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" t="s">
-        <v>62</v>
-      </c>
-      <c r="O15" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1521,10 +1569,10 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -1533,10 +1581,10 @@
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -1548,30 +1596,30 @@
         <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
         <v>113</v>
       </c>
-      <c r="B17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -1580,10 +1628,10 @@
         <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -1595,18 +1643,18 @@
         <v>18</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1615,10 +1663,10 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
@@ -1630,77 +1678,77 @@
         <v>119</v>
       </c>
       <c r="K18" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" t="s">
         <v>120</v>
       </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>121</v>
-      </c>
-      <c r="O18" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
         <v>123</v>
       </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
         <v>124</v>
       </c>
-      <c r="H19" t="s">
-        <v>74</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>125</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" t="s">
         <v>126</v>
-      </c>
-      <c r="L19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" t="s">
-        <v>127</v>
-      </c>
-      <c r="O19" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1709,10 +1757,10 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -1721,22 +1769,210 @@
         <v>18</v>
       </c>
       <c r="J20" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" t="s">
+        <v>130</v>
+      </c>
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
+        <v>90</v>
+      </c>
+      <c r="O20" t="s">
         <v>131</v>
       </c>
-      <c r="K20" t="s">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>132</v>
       </c>
-      <c r="L20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
         <v>133</v>
       </c>
-      <c r="O20" t="s">
+      <c r="G21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
         <v>134</v>
+      </c>
+      <c r="K21" t="s">
+        <v>130</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
+        <v>142</v>
+      </c>
+      <c r="K23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" t="s">
+        <v>49</v>
+      </c>
+      <c r="O23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" t="s">
+        <v>149</v>
+      </c>
+      <c r="O24" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8AF51CC-3FEC-4729-B862-0349BC56BC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D26DBA5-7E70-4D38-8937-BC95061524A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="132">
   <si>
     <t>Time</t>
   </si>
@@ -411,63 +411,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
-  </si>
-  <si>
-    <t>03/29/2026 12:25:48 AM</t>
-  </si>
-  <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
-    <t>299 West Ada Street, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445380e-371f-569c-bea6-06003c4f8020</t>
-  </si>
-  <si>
-    <t>03/27/2026 10:44:31 AM</t>
-  </si>
-  <si>
-    <t>2000 South FM 1788, Midland, TX, 79711</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ff7-f025-5aab-90d6-655800596967</t>
-  </si>
-  <si>
-    <t>03/27/2026 5:29:47 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Congested, Night</t>
-  </si>
-  <si>
-    <t>103 West 42nd Street (Chris Kyle Memorial Highway), Odessa, TX, 79764</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ed7-ccbf-5d9f-84c5-9eb2870bb772</t>
-  </si>
-  <si>
-    <t>03/26/2026 1:22:56 PM</t>
-  </si>
-  <si>
-    <t>Construction, Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>I 20, Warfield, TX, 79711</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b62-9c23-563a-8aba-f9ff827fee94</t>
   </si>
 </sst>
 </file>
@@ -844,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1787,194 +1730,6 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" t="s">
-        <v>130</v>
-      </c>
-      <c r="L21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>136</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>137</v>
-      </c>
-      <c r="K22" t="s">
-        <v>138</v>
-      </c>
-      <c r="L22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" t="s">
-        <v>141</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>142</v>
-      </c>
-      <c r="K23" t="s">
-        <v>143</v>
-      </c>
-      <c r="L23" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" t="s">
-        <v>49</v>
-      </c>
-      <c r="O23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" t="s">
-        <v>66</v>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s">
-        <v>147</v>
-      </c>
-      <c r="K24" t="s">
-        <v>148</v>
-      </c>
-      <c r="L24" t="s">
-        <v>18</v>
-      </c>
-      <c r="M24" t="s">
-        <v>18</v>
-      </c>
-      <c r="N24" t="s">
-        <v>149</v>
-      </c>
-      <c r="O24" t="s">
-        <v>150</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D26DBA5-7E70-4D38-8937-BC95061524A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B980D47-3615-4A75-B3CC-8F39D132A70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="147">
   <si>
     <t>Time</t>
   </si>
@@ -62,30 +62,105 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/02/2026 12:16:01 PM</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Leonard Ramirez</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Increased Sensitivity, Parking Lot, Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>US Hwy 285, Orla, TX, 79770</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523d4-9362-51e1-9cf2-cd81560cb8a1</t>
+  </si>
+  <si>
+    <t>06/30/2026 11:37:39 PM</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>James Jenkins</t>
+  </si>
+  <si>
+    <t>Heavy Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>North Grant Avenue, Odessa, TX, 79761</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451bf7-e831-554a-abc2-2719eb6b5e98</t>
+  </si>
+  <si>
+    <t>06/30/2026 4:21:07 AM</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>Steve Perkins</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Moderate Traffic, Night</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Liz Guthrie</t>
+  </si>
+  <si>
+    <t>I 20, West Odessa, TX, 79763</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544517d5-1252-501b-8be2-fd331f2067de</t>
+  </si>
+  <si>
     <t>06/18/2026 7:16:38 PM</t>
   </si>
   <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Leonard Ramirez</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
     <t>Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>East 2nd Street, Odessa, TX, 79761</t>
   </si>
   <si>
@@ -104,9 +179,6 @@
     <t>I 20;TX 158, Midland, TX, 79706</t>
   </si>
   <si>
-    <t>54</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d64f-baab-561e-9e3f-7ec3d8e646be</t>
   </si>
   <si>
@@ -152,9 +224,6 @@
     <t>06/12/2026 9:30:43 AM</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Construction, Moderate Traffic</t>
   </si>
   <si>
@@ -197,9 +266,6 @@
     <t>West 13th Street, Odessa, TX, 79761</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>0.59</t>
   </si>
   <si>
@@ -215,9 +281,6 @@
     <t>Rodney Salcido</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>FM 181, JY Ranch, TX</t>
   </si>
   <si>
@@ -356,9 +419,6 @@
     <t>Nicholas Rodecap</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Slightly Drowsy, Light Traffic, Night</t>
   </si>
   <si>
@@ -396,21 +456,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
-  </si>
-  <si>
-    <t>04/02/2026 6:07:12 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Moderate Traffic, Night</t>
-  </si>
-  <si>
-    <t>South Grant Avenue, Odessa, TX, 79761</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454de0-3354-56cf-ad33-b20d74fcd4ea</t>
   </si>
 </sst>
 </file>
@@ -787,10 +832,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -837,7 +882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -878,21 +923,21 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -901,10 +946,10 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -913,10 +958,10 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -928,18 +973,18 @@
         <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -948,22 +993,22 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -972,15 +1017,15 @@
         <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -995,10 +1040,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1007,10 +1052,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1022,12 +1067,12 @@
         <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -1042,10 +1087,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1054,10 +1099,10 @@
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1066,21 +1111,21 @@
         <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1089,10 +1134,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1101,10 +1146,10 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1113,21 +1158,21 @@
         <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="O7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1136,10 +1181,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1148,10 +1193,10 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1160,21 +1205,21 @@
         <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1183,22 +1228,22 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L9" t="s">
         <v>18</v>
@@ -1207,21 +1252,21 @@
         <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="O9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1230,10 +1275,10 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -1242,10 +1287,10 @@
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L10" t="s">
         <v>18</v>
@@ -1257,89 +1302,89 @@
         <v>18</v>
       </c>
       <c r="O10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>78</v>
-      </c>
-      <c r="K11" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
@@ -1351,18 +1396,18 @@
         <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1371,10 +1416,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1383,10 +1428,10 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1395,68 +1440,68 @@
         <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" t="s">
+        <v>101</v>
+      </c>
+      <c r="O14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s">
         <v>92</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C15" t="s">
         <v>93</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" t="s">
-        <v>97</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1468,19 +1513,19 @@
         <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1492,18 +1537,18 @@
         <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1515,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -1524,10 +1569,10 @@
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -1536,21 +1581,21 @@
         <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="O16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1559,10 +1604,10 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -1571,10 +1616,10 @@
         <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="K17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -1586,18 +1631,18 @@
         <v>18</v>
       </c>
       <c r="O17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1606,22 +1651,22 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K18" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -1630,21 +1675,21 @@
         <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="O18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -1653,10 +1698,10 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
@@ -1665,10 +1710,10 @@
         <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -1680,18 +1725,18 @@
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1700,10 +1745,10 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -1712,10 +1757,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K20" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s">
         <v>18</v>
@@ -1724,10 +1769,104 @@
         <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
-        <v>131</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>139</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" t="s">
+        <v>140</v>
+      </c>
+      <c r="O21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
+        <v>143</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>144</v>
+      </c>
+      <c r="K22" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B980D47-3615-4A75-B3CC-8F39D132A70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CC36CA4-4BAC-4D7F-92BC-3FC91D901430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="157">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>07/02/2026 12:16:01 PM</t>
+    <t>07/07/2026 10:46:28 AM</t>
   </si>
   <si>
     <t>516</t>
@@ -77,15 +77,69 @@
     <t>HAAS Alert</t>
   </si>
   <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Chris Kyle Memorial Highway, Odessa, TX, 79765</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453d79-4f43-5a5c-86fc-36388ba40a4c</t>
+  </si>
+  <si>
+    <t>07/06/2026 7:13:02 AM</t>
+  </si>
+  <si>
+    <t>Rocky Lane Road, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445378f-8ba0-5472-93b4-d9cc7897dd7e</t>
+  </si>
+  <si>
+    <t>07/05/2026 5:55:41 PM</t>
+  </si>
+  <si>
+    <t>Ray C. Stoker, Jr. Memorial Highway, Odessa, TX, 79765</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544534b5-8ecb-52c1-88e4-bf248d0e4ab9</t>
+  </si>
+  <si>
+    <t>07/04/2026 4:51:27 PM</t>
+  </si>
+  <si>
+    <t>State Highway 191 East, Odessa, TX, 79765</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452f54-63ff-5e52-9198-c72bf69064fd</t>
+  </si>
+  <si>
+    <t>07/02/2026 11:16:01 AM</t>
+  </si>
+  <si>
     <t>Harsh Brake</t>
   </si>
   <si>
     <t>Increased Sensitivity, Parking Lot, Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>US Hwy 285, Orla, TX, 79770</t>
   </si>
   <si>
@@ -98,7 +152,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523d4-9362-51e1-9cf2-cd81560cb8a1</t>
   </si>
   <si>
-    <t>06/30/2026 11:37:39 PM</t>
+    <t>06/30/2026 10:37:39 PM</t>
   </si>
   <si>
     <t>607</t>
@@ -122,7 +176,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451bf7-e831-554a-abc2-2719eb6b5e98</t>
   </si>
   <si>
-    <t>06/30/2026 4:21:07 AM</t>
+    <t>06/30/2026 3:21:07 AM</t>
   </si>
   <si>
     <t>581</t>
@@ -152,15 +206,12 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544517d5-1252-501b-8be2-fd331f2067de</t>
   </si>
   <si>
-    <t>06/18/2026 7:16:38 PM</t>
+    <t>06/18/2026 6:16:38 PM</t>
   </si>
   <si>
     <t>Mobile Usage</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>East 2nd Street, Odessa, TX, 79761</t>
   </si>
   <si>
@@ -170,10 +221,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd3c-9fc7-5cc9-9733-6ab33059920f</t>
   </si>
   <si>
-    <t>06/17/2026 11:00:09 AM</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
+    <t>06/17/2026 10:00:09 AM</t>
   </si>
   <si>
     <t>I 20;TX 158, Midland, TX, 79706</t>
@@ -182,7 +230,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d64f-baab-561e-9e3f-7ec3d8e646be</t>
   </si>
   <si>
-    <t>06/16/2026 3:47:27 AM</t>
+    <t>06/16/2026 2:47:27 AM</t>
   </si>
   <si>
     <t>604</t>
@@ -209,7 +257,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cf9d-382b-5dbe-b1df-13b8573088b3</t>
   </si>
   <si>
-    <t>06/15/2026 2:31:48 PM</t>
+    <t>06/15/2026 1:31:48 PM</t>
   </si>
   <si>
     <t>FM 181, 17.6 mi SW Seminole, Gaines County, TX</t>
@@ -221,7 +269,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ccc4-c870-5d84-9a44-42750cb7b81f</t>
   </si>
   <si>
-    <t>06/12/2026 9:30:43 AM</t>
+    <t>06/12/2026 8:30:43 AM</t>
   </si>
   <si>
     <t>Construction, Moderate Traffic</t>
@@ -230,16 +278,13 @@
     <t>FM 181, 14.6 mi WSW Andrews, Andrews County, TX</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>0.65</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3e-0c9c-5ba1-937d-ac0319ff2062</t>
   </si>
   <si>
-    <t>06/08/2026 7:17:58 PM</t>
+    <t>06/08/2026 6:17:58 PM</t>
   </si>
   <si>
     <t>Following Distance</t>
@@ -254,7 +299,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a9be-42c9-5b4d-940e-aa0d0bc99ce7</t>
   </si>
   <si>
-    <t>06/07/2026 10:08:28 PM</t>
+    <t>06/07/2026 9:08:28 PM</t>
   </si>
   <si>
     <t>603</t>
@@ -272,7 +317,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a533-ff4c-569f-b5ff-375990f785e7</t>
   </si>
   <si>
-    <t>06/05/2026 8:46:40 AM</t>
+    <t>06/05/2026 7:46:40 AM</t>
   </si>
   <si>
     <t>583</t>
@@ -290,7 +335,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459809-35c1-59bb-a9f3-05aab0fdce0a</t>
   </si>
   <si>
-    <t>06/03/2026 1:17:18 PM</t>
+    <t>06/03/2026 12:17:18 PM</t>
   </si>
   <si>
     <t>517</t>
@@ -308,7 +353,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458eb4-436d-5442-b353-f930bce641f0</t>
   </si>
   <si>
-    <t>06/02/2026 3:36:18 PM</t>
+    <t>06/02/2026 2:36:18 PM</t>
   </si>
   <si>
     <t>Construction, Light Traffic</t>
@@ -326,7 +371,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458a0d-2877-5170-a4a3-3dc86ca45e81</t>
   </si>
   <si>
-    <t>06/02/2026 3:17:57 PM</t>
+    <t>06/02/2026 2:17:57 PM</t>
   </si>
   <si>
     <t>South Grandview Avenue, Odessa, TX, 79761</t>
@@ -338,7 +383,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544589fc-5cea-50cb-8128-35cb402cd18d</t>
   </si>
   <si>
-    <t>05/29/2026 12:01:35 PM</t>
+    <t>05/29/2026 11:01:35 AM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic</t>
@@ -356,7 +401,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574af-244b-51d9-936e-a9522a16ec6e</t>
   </si>
   <si>
-    <t>05/29/2026 8:13:59 AM</t>
+    <t>05/29/2026 7:13:59 AM</t>
   </si>
   <si>
     <t>277</t>
@@ -377,7 +422,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544573de-c59e-58a0-85bc-46a91e8c6b76</t>
   </si>
   <si>
-    <t>05/18/2026 3:55:26 PM</t>
+    <t>05/18/2026 2:55:26 PM</t>
   </si>
   <si>
     <t>672</t>
@@ -392,7 +437,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453cdf-486f-5a10-b9ac-9478e42505a0</t>
   </si>
   <si>
-    <t>05/09/2026 10:01:35 PM</t>
+    <t>05/09/2026 9:01:35 PM</t>
   </si>
   <si>
     <t>673</t>
@@ -410,7 +455,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450fd5-44b4-5027-89b3-440a08cb2c22</t>
   </si>
   <si>
-    <t>05/09/2026 2:20:47 AM</t>
+    <t>05/09/2026 1:20:47 AM</t>
   </si>
   <si>
     <t>585</t>
@@ -431,7 +476,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b9c-3845-5a7e-82f1-12d91a117dfe</t>
   </si>
   <si>
-    <t>05/01/2026 2:14:13 PM</t>
+    <t>05/01/2026 1:14:13 PM</t>
   </si>
   <si>
     <t>I 20-E Business, Midland, TX, 79712</t>
@@ -441,21 +486,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e4f6-81e7-5c75-8318-c6dfd58c5b0c</t>
-  </si>
-  <si>
-    <t>04/07/2026 7:34:13 PM</t>
-  </si>
-  <si>
-    <t>Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>3175 Tanglewood Lane, Odessa, TX, 79762</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456a82-d855-59d6-ae18-0d427ee97430</t>
   </si>
 </sst>
 </file>
@@ -832,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -923,21 +953,21 @@
         <v>18</v>
       </c>
       <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -946,10 +976,10 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -958,10 +988,10 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -973,18 +1003,18 @@
         <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -993,22 +1023,22 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -1020,12 +1050,12 @@
         <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -1040,10 +1070,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1052,10 +1082,10 @@
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1067,12 +1097,12 @@
         <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -1087,10 +1117,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1099,10 +1129,10 @@
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1111,21 +1141,21 @@
         <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1134,10 +1164,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1146,10 +1176,10 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1158,21 +1188,21 @@
         <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1181,22 +1211,22 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1208,12 +1238,12 @@
         <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -1228,10 +1258,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1240,10 +1270,10 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L9" t="s">
         <v>18</v>
@@ -1252,15 +1282,15 @@
         <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -1275,10 +1305,10 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -1287,10 +1317,10 @@
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="L10" t="s">
         <v>18</v>
@@ -1302,18 +1332,18 @@
         <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1322,10 +1352,10 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1334,10 +1364,10 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -1346,21 +1376,21 @@
         <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1369,22 +1399,22 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
@@ -1396,18 +1426,18 @@
         <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1416,10 +1446,10 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1428,10 +1458,10 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1440,21 +1470,21 @@
         <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1463,22 +1493,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1487,21 +1517,21 @@
         <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1510,10 +1540,10 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1522,10 +1552,10 @@
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1534,21 +1564,21 @@
         <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="O15" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1557,22 +1587,22 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -1581,21 +1611,21 @@
         <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1604,10 +1634,10 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -1616,10 +1646,10 @@
         <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="K17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -1631,18 +1661,18 @@
         <v>18</v>
       </c>
       <c r="O17" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1651,22 +1681,22 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K18" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -1675,21 +1705,21 @@
         <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -1698,10 +1728,10 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
@@ -1710,10 +1740,10 @@
         <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K19" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -1725,18 +1755,18 @@
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1745,10 +1775,10 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -1757,10 +1787,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K20" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="L20" t="s">
         <v>18</v>
@@ -1769,21 +1799,21 @@
         <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="O20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -1792,10 +1822,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -1804,10 +1834,10 @@
         <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="K21" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s">
         <v>18</v>
@@ -1816,57 +1846,198 @@
         <v>18</v>
       </c>
       <c r="N21" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="O21" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" t="s">
         <v>142</v>
       </c>
-      <c r="B22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
         <v>143</v>
       </c>
-      <c r="H22" t="s">
+      <c r="K23" t="s">
+        <v>144</v>
+      </c>
+      <c r="L23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
+        <v>149</v>
+      </c>
+      <c r="H24" t="s">
         <v>22</v>
       </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>144</v>
-      </c>
-      <c r="K22" t="s">
-        <v>145</v>
-      </c>
-      <c r="L22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" t="s">
-        <v>146</v>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" t="s">
+        <v>155</v>
+      </c>
+      <c r="O25" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CC36CA4-4BAC-4D7F-92BC-3FC91D901430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9917F57-9EF7-49C8-81F7-8770BE50E9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="175">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,99 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/16/2026 7:34:56 PM</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>Nathan Roe</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>4115 Andrews Highway, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456db6-5eb6-55c5-8b84-915c033388b9</t>
+  </si>
+  <si>
+    <t>07/14/2026 1:23:35 PM</t>
+  </si>
+  <si>
+    <t>North FM 179, 18.4 mi ESE Littlefield, County Line, TX</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456215-ae89-594b-9a82-cfc1010fbd08</t>
+  </si>
+  <si>
+    <t>07/10/2026 6:19:25 PM</t>
+  </si>
+  <si>
+    <t>591</t>
+  </si>
+  <si>
+    <t>Nicholas Rodecap</t>
+  </si>
+  <si>
+    <t>Heavy Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>NM HWY 128, Ochoa, NM</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454e8b-14be-58f5-a093-067c2c04a6de</t>
+  </si>
+  <si>
+    <t>07/10/2026 1:59:56 PM</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Colby Miller</t>
+  </si>
+  <si>
+    <t>Crash</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>East Highway 80, Odessa, TX, 79762</t>
+  </si>
+  <si>
+    <t>5.63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454d9d-8413-585d-9ad3-24ea0cb92359</t>
+  </si>
+  <si>
     <t>07/07/2026 10:46:28 AM</t>
   </si>
   <si>
@@ -71,21 +164,9 @@
     <t>Leonard Ramirez</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Obstructed Camera</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>Chris Kyle Memorial Highway, Odessa, TX, 79765</t>
   </si>
   <si>
@@ -143,9 +224,6 @@
     <t>US Hwy 285, Orla, TX, 79770</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>0.66</t>
   </si>
   <si>
@@ -161,12 +239,6 @@
     <t>James Jenkins</t>
   </si>
   <si>
-    <t>Heavy Speeding</t>
-  </si>
-  <si>
-    <t>Speed Sign Verified</t>
-  </si>
-  <si>
     <t>North Grant Avenue, Odessa, TX, 79761</t>
   </si>
   <si>
@@ -233,21 +305,12 @@
     <t>06/16/2026 2:47:27 AM</t>
   </si>
   <si>
-    <t>604</t>
-  </si>
-  <si>
-    <t>Colby Miller</t>
-  </si>
-  <si>
     <t>Harsh Turn</t>
   </si>
   <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
-    <t>East Highway 80, Odessa, TX, 79762</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -293,9 +356,6 @@
     <t>I 20, Penwell, TX</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a9be-42c9-5b4d-940e-aa0d0bc99ce7</t>
   </si>
   <si>
@@ -341,9 +401,6 @@
     <t>517</t>
   </si>
   <si>
-    <t>Nathan Roe</t>
-  </si>
-  <si>
     <t>Northwest Loop 338, Westside, TX, 79767</t>
   </si>
   <si>
@@ -459,9 +516,6 @@
   </si>
   <si>
     <t>585</t>
-  </si>
-  <si>
-    <t>Nicholas Rodecap</t>
   </si>
   <si>
     <t>Slightly Drowsy, Light Traffic, Night</t>
@@ -862,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -932,25 +986,25 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
         <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
       </c>
       <c r="N2" t="s">
         <v>18</v>
@@ -982,7 +1036,7 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
@@ -997,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N3" t="s">
         <v>18</v>
@@ -1011,10 +1065,10 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1023,22 +1077,22 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -1050,18 +1104,18 @@
         <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -1070,22 +1124,22 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1094,21 +1148,21 @@
         <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="O5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1117,22 +1171,22 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1141,21 +1195,21 @@
         <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1164,22 +1218,22 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1191,18 +1245,18 @@
         <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1211,125 +1265,125 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
         <v>58</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>59</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
         <v>60</v>
-      </c>
-      <c r="K8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" t="s">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
         <v>64</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
         <v>69</v>
-      </c>
-      <c r="K10" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
@@ -1352,69 +1406,69 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
         <v>74</v>
       </c>
-      <c r="G11" t="s">
+      <c r="K11" t="s">
         <v>75</v>
       </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
         <v>76</v>
-      </c>
-      <c r="K11" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
-        <v>78</v>
-      </c>
-      <c r="O11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
         <v>80</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
@@ -1426,18 +1480,18 @@
         <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -1446,22 +1500,22 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1470,21 +1524,21 @@
         <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1493,22 +1547,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K14" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1520,42 +1574,42 @@
         <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="K15" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1564,210 +1618,210 @@
         <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
         <v>102</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>103</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" t="s">
         <v>104</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" t="s">
         <v>106</v>
       </c>
-      <c r="B17" t="s">
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
         <v>107</v>
       </c>
-      <c r="C17" t="s">
+      <c r="K17" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
         <v>108</v>
       </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="O17" t="s">
         <v>109</v>
-      </c>
-      <c r="K17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
         <v>112</v>
       </c>
-      <c r="B18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="K18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" t="s">
         <v>113</v>
-      </c>
-      <c r="H18" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>114</v>
-      </c>
-      <c r="K18" t="s">
-        <v>115</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" t="s">
-        <v>116</v>
-      </c>
-      <c r="O18" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
         <v>118</v>
       </c>
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="O19" t="s">
         <v>119</v>
-      </c>
-      <c r="K19" t="s">
-        <v>120</v>
-      </c>
-      <c r="L19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" t="s">
         <v>122</v>
       </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
@@ -1775,269 +1829,457 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
         <v>123</v>
       </c>
-      <c r="H20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>124</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" t="s">
         <v>125</v>
-      </c>
-      <c r="L20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" t="s">
-        <v>126</v>
-      </c>
-      <c r="O20" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
         <v>128</v>
       </c>
-      <c r="B21" t="s">
+      <c r="K21" t="s">
         <v>129</v>
       </c>
-      <c r="C21" t="s">
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
         <v>130</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s">
-        <v>65</v>
-      </c>
-      <c r="K21" t="s">
-        <v>133</v>
-      </c>
-      <c r="L21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" t="s">
+        <v>132</v>
+      </c>
+      <c r="H22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" t="s">
         <v>135</v>
       </c>
-      <c r="B22" t="s">
+      <c r="O22" t="s">
         <v>136</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>137</v>
-      </c>
-      <c r="K22" t="s">
-        <v>138</v>
-      </c>
-      <c r="L22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
+        <v>138</v>
+      </c>
+      <c r="K23" t="s">
+        <v>139</v>
+      </c>
+      <c r="L23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" t="s">
         <v>140</v>
-      </c>
-      <c r="B23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C23" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>143</v>
-      </c>
-      <c r="K23" t="s">
-        <v>144</v>
-      </c>
-      <c r="L23" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" t="s">
+        <v>144</v>
+      </c>
+      <c r="L24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" t="s">
+        <v>145</v>
+      </c>
+      <c r="O24" t="s">
         <v>146</v>
-      </c>
-      <c r="B24" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24" t="s">
-        <v>149</v>
-      </c>
-      <c r="H24" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s">
-        <v>150</v>
-      </c>
-      <c r="K24" t="s">
-        <v>151</v>
-      </c>
-      <c r="L24" t="s">
-        <v>18</v>
-      </c>
-      <c r="M24" t="s">
-        <v>18</v>
-      </c>
-      <c r="N24" t="s">
-        <v>18</v>
-      </c>
-      <c r="O24" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" t="s">
+        <v>152</v>
+      </c>
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" t="s">
         <v>153</v>
       </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>154</v>
       </c>
-      <c r="K25" t="s">
+      <c r="B26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K26" t="s">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
+        <v>162</v>
+      </c>
+      <c r="K27" t="s">
+        <v>163</v>
+      </c>
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>168</v>
+      </c>
+      <c r="K28" t="s">
+        <v>169</v>
+      </c>
+      <c r="L28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" t="s">
         <v>42</v>
       </c>
-      <c r="L25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N25" t="s">
-        <v>155</v>
-      </c>
-      <c r="O25" t="s">
-        <v>156</v>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s">
+        <v>172</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" t="s">
+        <v>18</v>
+      </c>
+      <c r="M29" t="s">
+        <v>18</v>
+      </c>
+      <c r="N29" t="s">
+        <v>173</v>
+      </c>
+      <c r="O29" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9917F57-9EF7-49C8-81F7-8770BE50E9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFFA4C6A-3BC3-4A42-B476-1258C5B3C09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="179">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,40 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>07/16/2026 7:34:56 PM</t>
+    <t>07/22/2026 9:33:16 PM</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>Steve Perkins</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HAAS Alert</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Kell Freeway, Wichita Falls, TX, 76301</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458d3f-cd68-51eb-955c-e29b358afe54</t>
+  </si>
+  <si>
+    <t>07/16/2026 6:34:56 PM</t>
   </si>
   <si>
     <t>518</t>
@@ -71,18 +104,9 @@
     <t>Nathan Roe</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HAAS Alert</t>
-  </si>
-  <si>
     <t>Inattentive Driving</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>4115 Andrews Highway, Odessa, TX, 79762</t>
   </si>
   <si>
@@ -95,7 +119,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456db6-5eb6-55c5-8b84-915c033388b9</t>
   </si>
   <si>
-    <t>07/14/2026 1:23:35 PM</t>
+    <t>07/14/2026 12:23:35 PM</t>
   </si>
   <si>
     <t>North FM 179, 18.4 mi ESE Littlefield, County Line, TX</t>
@@ -107,7 +131,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456215-ae89-594b-9a82-cfc1010fbd08</t>
   </si>
   <si>
-    <t>07/10/2026 6:19:25 PM</t>
+    <t>07/10/2026 5:19:25 PM</t>
   </si>
   <si>
     <t>591</t>
@@ -131,7 +155,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454e8b-14be-58f5-a093-067c2c04a6de</t>
   </si>
   <si>
-    <t>07/10/2026 1:59:56 PM</t>
+    <t>07/10/2026 12:59:56 PM</t>
   </si>
   <si>
     <t>604</t>
@@ -155,7 +179,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454d9d-8413-585d-9ad3-24ea0cb92359</t>
   </si>
   <si>
-    <t>07/07/2026 10:46:28 AM</t>
+    <t>07/07/2026 9:46:28 AM</t>
   </si>
   <si>
     <t>516</t>
@@ -176,7 +200,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453d79-4f43-5a5c-86fc-36388ba40a4c</t>
   </si>
   <si>
-    <t>07/06/2026 7:13:02 AM</t>
+    <t>07/06/2026 6:13:02 AM</t>
   </si>
   <si>
     <t>Rocky Lane Road, Odessa, TX, 79762</t>
@@ -188,7 +212,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445378f-8ba0-5472-93b4-d9cc7897dd7e</t>
   </si>
   <si>
-    <t>07/05/2026 5:55:41 PM</t>
+    <t>07/05/2026 4:55:41 PM</t>
   </si>
   <si>
     <t>Ray C. Stoker, Jr. Memorial Highway, Odessa, TX, 79765</t>
@@ -200,7 +224,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544534b5-8ecb-52c1-88e4-bf248d0e4ab9</t>
   </si>
   <si>
-    <t>07/04/2026 4:51:27 PM</t>
+    <t>07/04/2026 3:51:27 PM</t>
   </si>
   <si>
     <t>State Highway 191 East, Odessa, TX, 79765</t>
@@ -212,7 +236,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452f54-63ff-5e52-9198-c72bf69064fd</t>
   </si>
   <si>
-    <t>07/02/2026 11:16:01 AM</t>
+    <t>07/02/2026 10:16:01 AM</t>
   </si>
   <si>
     <t>Harsh Brake</t>
@@ -230,7 +254,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523d4-9362-51e1-9cf2-cd81560cb8a1</t>
   </si>
   <si>
-    <t>06/30/2026 10:37:39 PM</t>
+    <t>06/30/2026 9:37:39 PM</t>
   </si>
   <si>
     <t>607</t>
@@ -248,16 +272,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451bf7-e831-554a-abc2-2719eb6b5e98</t>
   </si>
   <si>
-    <t>06/30/2026 3:21:07 AM</t>
-  </si>
-  <si>
-    <t>581</t>
-  </si>
-  <si>
-    <t>Steve Perkins</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
+    <t>06/30/2026 2:21:07 AM</t>
   </si>
   <si>
     <t>Very Drowsy, Moderate Traffic, Night</t>
@@ -278,7 +293,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544517d5-1252-501b-8be2-fd331f2067de</t>
   </si>
   <si>
-    <t>06/18/2026 6:16:38 PM</t>
+    <t>06/18/2026 5:16:38 PM</t>
   </si>
   <si>
     <t>Mobile Usage</t>
@@ -293,7 +308,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd3c-9fc7-5cc9-9733-6ab33059920f</t>
   </si>
   <si>
-    <t>06/17/2026 10:00:09 AM</t>
+    <t>06/17/2026 9:00:09 AM</t>
   </si>
   <si>
     <t>I 20;TX 158, Midland, TX, 79706</t>
@@ -302,7 +317,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d64f-baab-561e-9e3f-7ec3d8e646be</t>
   </si>
   <si>
-    <t>06/16/2026 2:47:27 AM</t>
+    <t>06/16/2026 1:47:27 AM</t>
   </si>
   <si>
     <t>Harsh Turn</t>
@@ -320,7 +335,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cf9d-382b-5dbe-b1df-13b8573088b3</t>
   </si>
   <si>
-    <t>06/15/2026 1:31:48 PM</t>
+    <t>06/15/2026 12:31:48 PM</t>
   </si>
   <si>
     <t>FM 181, 17.6 mi SW Seminole, Gaines County, TX</t>
@@ -332,7 +347,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ccc4-c870-5d84-9a44-42750cb7b81f</t>
   </si>
   <si>
-    <t>06/12/2026 8:30:43 AM</t>
+    <t>06/12/2026 7:30:43 AM</t>
   </si>
   <si>
     <t>Construction, Moderate Traffic</t>
@@ -347,7 +362,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3e-0c9c-5ba1-937d-ac0319ff2062</t>
   </si>
   <si>
-    <t>06/08/2026 6:17:58 PM</t>
+    <t>06/08/2026 5:17:58 PM</t>
   </si>
   <si>
     <t>Following Distance</t>
@@ -359,7 +374,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a9be-42c9-5b4d-940e-aa0d0bc99ce7</t>
   </si>
   <si>
-    <t>06/07/2026 9:08:28 PM</t>
+    <t>06/07/2026 8:08:28 PM</t>
   </si>
   <si>
     <t>603</t>
@@ -377,7 +392,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a533-ff4c-569f-b5ff-375990f785e7</t>
   </si>
   <si>
-    <t>06/05/2026 7:46:40 AM</t>
+    <t>06/05/2026 6:46:40 AM</t>
   </si>
   <si>
     <t>583</t>
@@ -395,7 +410,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459809-35c1-59bb-a9f3-05aab0fdce0a</t>
   </si>
   <si>
-    <t>06/03/2026 12:17:18 PM</t>
+    <t>06/03/2026 11:17:18 AM</t>
   </si>
   <si>
     <t>517</t>
@@ -410,7 +425,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458eb4-436d-5442-b353-f930bce641f0</t>
   </si>
   <si>
-    <t>06/02/2026 2:36:18 PM</t>
+    <t>06/02/2026 1:36:18 PM</t>
   </si>
   <si>
     <t>Construction, Light Traffic</t>
@@ -428,7 +443,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458a0d-2877-5170-a4a3-3dc86ca45e81</t>
   </si>
   <si>
-    <t>06/02/2026 2:17:57 PM</t>
+    <t>06/02/2026 1:17:57 PM</t>
   </si>
   <si>
     <t>South Grandview Avenue, Odessa, TX, 79761</t>
@@ -440,7 +455,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544589fc-5cea-50cb-8128-35cb402cd18d</t>
   </si>
   <si>
-    <t>05/29/2026 11:01:35 AM</t>
+    <t>05/29/2026 10:01:35 AM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic</t>
@@ -458,7 +473,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574af-244b-51d9-936e-a9522a16ec6e</t>
   </si>
   <si>
-    <t>05/29/2026 7:13:59 AM</t>
+    <t>05/29/2026 6:13:59 AM</t>
   </si>
   <si>
     <t>277</t>
@@ -479,7 +494,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544573de-c59e-58a0-85bc-46a91e8c6b76</t>
   </si>
   <si>
-    <t>05/18/2026 2:55:26 PM</t>
+    <t>05/18/2026 1:55:26 PM</t>
   </si>
   <si>
     <t>672</t>
@@ -488,13 +503,10 @@
     <t>11610 West Interstate 20, Warfield, TX, 79706</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453cdf-486f-5a10-b9ac-9478e42505a0</t>
   </si>
   <si>
-    <t>05/09/2026 9:01:35 PM</t>
+    <t>05/09/2026 8:01:35 PM</t>
   </si>
   <si>
     <t>673</t>
@@ -512,7 +524,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450fd5-44b4-5027-89b3-440a08cb2c22</t>
   </si>
   <si>
-    <t>05/09/2026 1:20:47 AM</t>
+    <t>05/09/2026 12:20:47 AM</t>
   </si>
   <si>
     <t>585</t>
@@ -530,7 +542,7 @@
     <t>https://cloud.samsara.com/o/6005545/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b9c-3845-5a7e-82f1-12d91a117dfe</t>
   </si>
   <si>
-    <t>05/01/2026 1:14:13 PM</t>
+    <t>05/01/2026 12:14:13 PM</t>
   </si>
   <si>
     <t>I 20-E Business, Midland, TX, 79712</t>
@@ -916,10 +928,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -966,7 +978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -986,25 +998,25 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
         <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
         <v>18</v>
@@ -1013,15 +1025,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -1030,60 +1042,60 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" t="s">
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1098,7 +1110,7 @@
         <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
         <v>18</v>
@@ -1107,7 +1119,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1130,7 +1142,7 @@
         <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1139,7 +1151,7 @@
         <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1148,13 +1160,13 @@
         <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="O5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1174,342 +1186,342 @@
         <v>49</v>
       </c>
       <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" t="s">
+        <v>71</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" t="s">
+        <v>77</v>
+      </c>
+      <c r="O11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
         <v>42</v>
       </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
-      </c>
-      <c r="K9" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" t="s">
-        <v>81</v>
-      </c>
       <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
         <v>82</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>83</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="K12" t="s">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>85</v>
       </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="H13" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="I13" t="s">
         <v>88</v>
-      </c>
-      <c r="G13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
       </c>
       <c r="J13" t="s">
         <v>89</v>
@@ -1530,15 +1542,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1547,22 +1559,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1574,18 +1586,18 @@
         <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1594,22 +1606,22 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1618,15 +1630,15 @@
         <v>18</v>
       </c>
       <c r="N15" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" t="s">
         <v>99</v>
       </c>
-      <c r="O15" t="s">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>101</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -1641,19 +1653,19 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="K16" t="s">
         <v>103</v>
@@ -1665,21 +1677,21 @@
         <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="O16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1688,13 +1700,13 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
         <v>18</v>
@@ -1703,7 +1715,7 @@
         <v>107</v>
       </c>
       <c r="K17" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -1712,21 +1724,21 @@
         <v>18</v>
       </c>
       <c r="N17" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="O17" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1735,13 +1747,13 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s">
         <v>111</v>
       </c>
-      <c r="G18" t="s">
-        <v>42</v>
-      </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
@@ -1750,7 +1762,7 @@
         <v>112</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -1759,36 +1771,36 @@
         <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
         <v>116</v>
       </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
         <v>18</v>
@@ -1797,7 +1809,7 @@
         <v>117</v>
       </c>
       <c r="K19" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -1806,69 +1818,69 @@
         <v>18</v>
       </c>
       <c r="N19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" t="s">
         <v>118</v>
       </c>
-      <c r="O19" t="s">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>120</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>121</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
         <v>122</v>
       </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>111</v>
-      </c>
-      <c r="G20" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" t="s">
         <v>123</v>
       </c>
-      <c r="K20" t="s">
+      <c r="O20" t="s">
         <v>124</v>
       </c>
-      <c r="L20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" t="s">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>126</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>127</v>
       </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
@@ -1876,13 +1888,13 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s">
         <v>18</v>
@@ -1906,15 +1918,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -1923,13 +1935,13 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
         <v>18</v>
@@ -1947,36 +1959,36 @@
         <v>18</v>
       </c>
       <c r="N22" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
         <v>135</v>
       </c>
-      <c r="O22" t="s">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
         <v>137</v>
       </c>
-      <c r="B23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" t="s">
-        <v>18</v>
-      </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
@@ -1994,21 +2006,21 @@
         <v>18</v>
       </c>
       <c r="N23" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="O23" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -2017,13 +2029,13 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
@@ -2041,89 +2053,89 @@
         <v>18</v>
       </c>
       <c r="N24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" t="s">
         <v>145</v>
       </c>
-      <c r="O24" t="s">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s">
         <v>147</v>
       </c>
-      <c r="B25" t="s">
+      <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s">
         <v>148</v>
       </c>
-      <c r="C25" t="s">
+      <c r="K25" t="s">
         <v>149</v>
       </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" t="s">
         <v>150</v>
       </c>
-      <c r="G25" t="s">
+      <c r="O25" t="s">
         <v>151</v>
       </c>
-      <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s">
-        <v>89</v>
-      </c>
-      <c r="K25" t="s">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>152</v>
       </c>
-      <c r="L25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N25" t="s">
-        <v>18</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="B26" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
         <v>154</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
         <v>155</v>
       </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>111</v>
-      </c>
       <c r="G26" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H26" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s">
         <v>157</v>
@@ -2141,7 +2153,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>159</v>
       </c>
@@ -2149,116 +2161,116 @@
         <v>160</v>
       </c>
       <c r="C27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
+        <v>137</v>
+      </c>
+      <c r="H27" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
         <v>161</v>
       </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" t="s">
         <v>162</v>
       </c>
-      <c r="K27" t="s">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>163</v>
       </c>
-      <c r="L27" t="s">
-        <v>18</v>
-      </c>
-      <c r="M27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N27" t="s">
-        <v>18</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="B28" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
         <v>165</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
         <v>166</v>
       </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>80</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="K28" t="s">
         <v>167</v>
       </c>
-      <c r="H28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" t="s">
         <v>168</v>
       </c>
-      <c r="K28" t="s">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>169</v>
       </c>
-      <c r="L28" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N28" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="B29" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
         <v>171</v>
       </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" t="s">
-        <v>42</v>
-      </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
@@ -2267,7 +2279,7 @@
         <v>172</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s">
         <v>18</v>
@@ -2276,10 +2288,57 @@
         <v>18</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="O29" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>176</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" t="s">
+        <v>177</v>
+      </c>
+      <c r="O30" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/25/2026 9:55:54 AM</t>
+          <t>08/06/2026 5:42:43 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -541,17 +541,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/22/2026 11:33:16 PM</t>
+          <t>08/05/2026 8:41:37 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/16/2026 8:34:56 PM</t>
+          <t>07/25/2026 9:55:54 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,17 +631,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/14/2026 2:23:35 PM</t>
+          <t>07/22/2026 11:33:16 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10/2026 2:59:56 PM</t>
+          <t>07/16/2026 8:34:56 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -711,25 +711,27 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>5.626</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/07/2026 11:46:28 AM</t>
+          <t>07/14/2026 2:23:35 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -740,7 +742,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -764,17 +766,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/06/2026 8:13:02 AM</t>
+          <t>07/10/2026 2:59:56 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -785,7 +787,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -799,17 +801,15 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" t="n">
+        <v>5.626</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/05/2026 6:55:41 PM</t>
+          <t>07/07/2026 11:46:28 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/04/2026 5:51:27 PM</t>
+          <t>07/06/2026 8:13:02 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02/2026 12:16:01 PM</t>
+          <t>07/05/2026 6:55:41 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -934,25 +934,27 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0.656</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30/2026 4:21:07 AM</t>
+          <t>07/04/2026 5:51:27 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -963,13 +965,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -987,7 +989,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/18/2026 7:16:38 PM</t>
+          <t>07/02/2026 12:16:01 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1008,7 +1010,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1022,27 +1024,25 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" t="n">
+        <v>0.656</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/30/2026 4:21:07 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1053,13 +1053,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1077,17 +1077,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/16/2026 3:47:27 AM</t>
+          <t>06/18/2026 7:16:38 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1112,15 +1112,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0.496</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/15/2026 2:31:48 PM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1165,17 +1167,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/12/2026 9:30:43 AM</t>
+          <t>06/16/2026 3:47:27 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1186,7 +1188,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1201,14 +1203,14 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>0.649</v>
+        <v>0.496</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/08/2026 7:17:58 PM</t>
+          <t>06/15/2026 2:31:48 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1231,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1253,17 +1255,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/07/2026 10:08:28 PM</t>
+          <t>06/12/2026 9:30:43 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Larry Richardson</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1289,24 +1291,24 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>0.593</v>
+        <v>0.649</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/05/2026 8:46:40 AM</t>
+          <t>06/08/2026 7:17:58 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1323,7 +1325,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1341,17 +1343,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/02/2026 3:36:18 PM</t>
+          <t>06/07/2026 10:08:28 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Larry Richardson</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1368,7 +1370,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1377,24 +1379,24 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>0.644</v>
+        <v>0.593</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05/29/2026 12:01:35 PM</t>
+          <t>06/05/2026 8:46:40 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Rodney Salcido</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1405,13 +1407,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1419,25 +1421,27 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>0.574</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05/29/2026 8:13:59 AM</t>
+          <t>06/02/2026 3:36:18 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hunter McDowell</t>
+          <t>Rodney Salcido</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1448,13 +1452,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1462,27 +1466,25 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" t="n">
+        <v>0.644</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05/18/2026 3:55:26 PM</t>
+          <t>05/29/2026 12:01:35 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1493,13 +1495,13 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1507,27 +1509,25 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N24" t="n">
+        <v>0.574</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05/09/2026 10:01:35 PM</t>
+          <t>05/29/2026 8:13:59 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Colby Smith</t>
+          <t>Hunter McDowell</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1562,17 +1562,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05/09/2026 2:20:47 AM</t>
+          <t>05/18/2026 3:55:26 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>672</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nicholas Rodecap</t>
+          <t>Rodney Salcido</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,19 +496,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/06/2026 5:42:43 PM</t>
+          <t>08/13/2026 7:48:31 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Leonard Ramirez</t>
-        </is>
-      </c>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -517,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -541,7 +537,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/05/2026 8:41:37 PM</t>
+          <t>08/12/2026 2:07:36 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -586,17 +582,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/25/2026 9:55:54 AM</t>
+          <t>08/12/2026 9:16:59 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -607,7 +603,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -621,27 +617,25 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N4" t="n">
+        <v>0.476</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22/2026 11:33:16 PM</t>
+          <t>08/11/2026 6:39:58 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -652,7 +646,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -666,27 +660,25 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" t="n">
+        <v>0.48</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/16/2026 8:34:56 PM</t>
+          <t>08/09/2026 11:31:56 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -697,7 +689,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -711,27 +703,25 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N6" t="n">
+        <v>0.475</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/14/2026 2:23:35 PM</t>
+          <t>08/06/2026 5:42:43 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -742,7 +732,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -766,17 +756,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10/2026 2:59:56 PM</t>
+          <t>08/05/2026 8:41:37 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -787,7 +777,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -801,25 +791,27 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>5.626</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/07/2026 11:46:28 AM</t>
+          <t>07/25/2026 9:55:54 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -830,7 +822,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -854,17 +846,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/06/2026 8:13:02 AM</t>
+          <t>07/22/2026 11:33:16 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -875,7 +867,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -899,17 +891,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/05/2026 6:55:41 PM</t>
+          <t>07/16/2026 8:34:56 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -920,7 +912,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -944,17 +936,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/04/2026 5:51:27 PM</t>
+          <t>07/14/2026 2:23:35 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -965,7 +957,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -989,17 +981,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02/2026 12:16:01 PM</t>
+          <t>07/10/2026 2:59:56 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1025,24 +1017,24 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>0.656</v>
+        <v>5.626</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30/2026 4:21:07 AM</t>
+          <t>07/07/2026 11:46:28 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1053,13 +1045,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1077,7 +1069,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/18/2026 7:16:38 PM</t>
+          <t>07/06/2026 8:13:02 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1098,7 +1090,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1122,7 +1114,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>07/05/2026 6:55:41 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1167,17 +1159,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/16/2026 3:47:27 AM</t>
+          <t>07/04/2026 5:51:27 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1188,7 +1180,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1202,15 +1194,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.496</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/15/2026 2:31:48 PM</t>
+          <t>07/02/2026 12:16:01 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1231,7 +1225,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1245,27 +1239,25 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N18" t="n">
+        <v>0.656</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/12/2026 9:30:43 AM</t>
+          <t>06/30/2026 4:21:07 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1276,13 +1268,13 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1290,15 +1282,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0.649</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/08/2026 7:17:58 PM</t>
+          <t>06/18/2026 7:16:38 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1319,7 +1313,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1343,17 +1337,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/07/2026 10:08:28 PM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Larry Richardson</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1364,7 +1358,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1378,25 +1372,27 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0.593</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/05/2026 8:46:40 AM</t>
+          <t>06/16/2026 3:47:27 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1407,13 +1403,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1421,27 +1417,25 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N22" t="n">
+        <v>0.496</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/02/2026 3:36:18 PM</t>
+          <t>06/15/2026 2:31:48 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1452,13 +1446,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1466,15 +1460,17 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>0.644</v>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05/29/2026 12:01:35 PM</t>
+          <t>06/12/2026 9:30:43 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1510,24 +1506,24 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>0.574</v>
+        <v>0.649</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05/29/2026 8:13:59 AM</t>
+          <t>06/08/2026 7:17:58 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hunter McDowell</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1562,17 +1558,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05/18/2026 3:55:26 PM</t>
+          <t>06/07/2026 10:08:28 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Larry Richardson</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1583,13 +1579,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1597,12 +1593,186 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N26" t="n">
+        <v>0.593</v>
       </c>
       <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>06/05/2026 8:46:40 AM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rodney Salcido</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>06/02/2026 3:36:18 PM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rodney Salcido</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>05/29/2026 12:01:35 PM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Leonard Ramirez</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>05/29/2026 8:13:59 AM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hunter McDowell</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,15 +496,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/13/2026 7:48:31 PM</t>
+          <t>08/19/2026 7:48:11 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Justin Williams</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -513,7 +517,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -537,17 +541,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/12/2026 2:07:36 PM</t>
+          <t>08/18/2026 6:20:27 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -558,7 +562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -582,12 +586,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/12/2026 9:16:59 AM</t>
+          <t>08/18/2026 6:29:37 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -618,24 +622,24 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0.476</v>
+        <v>0.413</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/11/2026 6:39:58 PM</t>
+          <t>08/17/2026 5:16:19 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -646,7 +650,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -661,24 +665,24 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.48</v>
+        <v>0.441</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/09/2026 11:31:56 AM</t>
+          <t>08/13/2026 7:48:31 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>641</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colin Huff</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -689,7 +693,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -703,25 +707,27 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>0.475</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/06/2026 5:42:43 PM</t>
+          <t>08/12/2026 2:07:36 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -732,7 +738,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -756,17 +762,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/05/2026 8:41:37 PM</t>
+          <t>08/12/2026 9:16:59 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -777,7 +783,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -791,27 +797,25 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" t="n">
+        <v>0.476</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/25/2026 9:55:54 AM</t>
+          <t>08/11/2026 6:39:58 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -822,7 +826,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -836,27 +840,25 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" t="n">
+        <v>0.48</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22/2026 11:33:16 PM</t>
+          <t>08/09/2026 11:31:56 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -867,7 +869,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -881,27 +883,25 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N10" t="n">
+        <v>0.475</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/16/2026 8:34:56 PM</t>
+          <t>08/06/2026 5:42:43 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -936,17 +936,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/14/2026 2:23:35 PM</t>
+          <t>08/05/2026 8:41:37 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -981,17 +981,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10/2026 2:59:56 PM</t>
+          <t>07/25/2026 9:55:54 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1016,25 +1016,27 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>5.626</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/07/2026 11:46:28 AM</t>
+          <t>07/22/2026 11:33:16 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1045,7 +1047,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1069,17 +1071,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/06/2026 8:13:02 AM</t>
+          <t>07/16/2026 8:34:56 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1090,7 +1092,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1114,17 +1116,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/05/2026 6:55:41 PM</t>
+          <t>07/14/2026 2:23:35 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1135,7 +1137,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1159,17 +1161,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/04/2026 5:51:27 PM</t>
+          <t>07/10/2026 2:59:56 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1180,7 +1182,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1194,17 +1196,15 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" t="n">
+        <v>5.626</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02/2026 12:16:01 PM</t>
+          <t>07/07/2026 11:46:28 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1239,25 +1239,27 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>0.656</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30/2026 4:21:07 AM</t>
+          <t>07/02/2026 12:16:01 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1268,13 +1270,13 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1282,27 +1284,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N19" t="n">
+        <v>0.656</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/18/2026 7:16:38 PM</t>
+          <t>06/30/2026 4:21:07 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1313,13 +1313,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/18/2026 7:16:38 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1382,17 +1382,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/16/2026 3:47:27 AM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1417,25 +1417,27 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>0.496</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/15/2026 2:31:48 PM</t>
+          <t>06/16/2026 3:47:27 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1446,7 +1448,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1460,17 +1462,15 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" t="n">
+        <v>0.496</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/12/2026 9:30:43 AM</t>
+          <t>06/15/2026 2:31:48 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1505,15 +1505,17 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>0.649</v>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/08/2026 7:17:58 PM</t>
+          <t>06/12/2026 9:30:43 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1536,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1548,27 +1550,25 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N25" t="n">
+        <v>0.649</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/07/2026 10:08:28 PM</t>
+          <t>06/08/2026 7:17:58 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Larry Richardson</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1593,25 +1593,27 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>0.593</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/05/2026 8:46:40 AM</t>
+          <t>06/07/2026 10:08:28 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Larry Richardson</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1622,13 +1624,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1636,17 +1638,15 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" t="n">
+        <v>0.593</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/02/2026 3:36:18 PM</t>
+          <t>06/05/2026 8:46:40 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1681,25 +1681,27 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>0.644</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05/29/2026 12:01:35 PM</t>
+          <t>06/02/2026 3:36:18 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Rodney Salcido</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1716,7 +1718,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1725,24 +1727,24 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>0.574</v>
+        <v>0.644</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05/29/2026 8:13:59 AM</t>
+          <t>05/29/2026 12:01:35 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hunter McDowell</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1753,7 +1755,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1767,12 +1769,55 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="N30" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>05/29/2026 8:13:59 AM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hunter McDowell</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,19 +496,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/19/2026 7:48:11 PM</t>
+          <t>08/23/2026 8:26:38 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Justin Williams</t>
-        </is>
-      </c>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,29 +527,23 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N2" t="n">
+        <v>0.445</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/18/2026 6:20:27 PM</t>
+          <t>08/23/2026 3:17:23 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Justin Williams</t>
-        </is>
-      </c>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -586,7 +576,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/18/2026 6:29:37 AM</t>
+          <t>08/22/2026 3:40:00 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,24 +612,24 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0.413</v>
+        <v>0.396</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/17/2026 5:16:19 PM</t>
+          <t>08/19/2026 7:48:11 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -664,25 +654,27 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>0.441</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/13/2026 7:48:31 PM</t>
+          <t>08/18/2026 6:20:27 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Colin Huff</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -693,7 +685,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -717,17 +709,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/12/2026 2:07:36 PM</t>
+          <t>08/18/2026 6:29:37 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -738,7 +730,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -752,27 +744,25 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N7" t="n">
+        <v>0.413</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/12/2026 9:16:59 AM</t>
+          <t>08/17/2026 5:16:19 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -783,7 +773,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -798,24 +788,24 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.476</v>
+        <v>0.441</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/11/2026 6:39:58 PM</t>
+          <t>08/13/2026 7:48:31 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>641</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Colin Huff</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -826,7 +816,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -840,15 +830,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0.48</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/09/2026 11:31:56 AM</t>
+          <t>08/12/2026 2:07:36 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -869,7 +861,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -883,25 +875,27 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>0.475</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/06/2026 5:42:43 PM</t>
+          <t>08/12/2026 9:16:59 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -912,7 +906,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -926,27 +920,25 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N11" t="n">
+        <v>0.476</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/05/2026 8:41:37 PM</t>
+          <t>08/11/2026 6:39:58 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -957,7 +949,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -971,27 +963,25 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" t="n">
+        <v>0.48</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/25/2026 9:55:54 AM</t>
+          <t>08/09/2026 11:31:56 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1002,7 +992,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1016,27 +1006,25 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" t="n">
+        <v>0.475</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22/2026 11:33:16 PM</t>
+          <t>08/06/2026 5:42:43 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1047,7 +1035,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1071,17 +1059,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/16/2026 8:34:56 PM</t>
+          <t>08/05/2026 8:41:37 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1092,7 +1080,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1116,7 +1104,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/14/2026 2:23:35 PM</t>
+          <t>07/25/2026 9:55:54 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1161,17 +1149,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/10/2026 2:59:56 PM</t>
+          <t>07/22/2026 11:33:16 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1182,7 +1170,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1196,25 +1184,27 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>5.626</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07/2026 11:46:28 AM</t>
+          <t>07/16/2026 8:34:56 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1225,7 +1215,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1249,17 +1239,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02/2026 12:16:01 PM</t>
+          <t>07/14/2026 2:23:35 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1270,7 +1260,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1284,25 +1274,27 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0.656</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30/2026 4:21:07 AM</t>
+          <t>07/10/2026 2:59:56 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1313,13 +1305,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1327,17 +1319,15 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" t="n">
+        <v>5.626</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/18/2026 7:16:38 PM</t>
+          <t>07/07/2026 11:46:28 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1348,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1382,7 +1372,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>07/02/2026 12:16:01 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1403,7 +1393,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1417,27 +1407,25 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N22" t="n">
+        <v>0.656</v>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/16/2026 3:47:27 AM</t>
+          <t>06/30/2026 4:21:07 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1448,13 +1436,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1462,15 +1450,17 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>0.496</v>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/15/2026 2:31:48 PM</t>
+          <t>06/18/2026 7:16:38 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1491,7 +1481,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1515,7 +1505,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/12/2026 9:30:43 AM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1536,7 +1526,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1550,25 +1540,27 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>0.649</v>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/08/2026 7:17:58 PM</t>
+          <t>06/16/2026 3:47:27 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1579,7 +1571,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1593,27 +1585,25 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N26" t="n">
+        <v>0.496</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/07/2026 10:08:28 PM</t>
+          <t>06/15/2026 2:31:48 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Larry Richardson</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1624,7 +1614,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1638,25 +1628,27 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>0.593</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/05/2026 8:46:40 AM</t>
+          <t>06/12/2026 9:30:43 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1667,13 +1659,13 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1681,27 +1673,25 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N28" t="n">
+        <v>0.649</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/02/2026 3:36:18 PM</t>
+          <t>06/08/2026 7:17:58 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1712,13 +1702,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1726,25 +1716,27 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>0.644</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05/29/2026 12:01:35 PM</t>
+          <t>06/07/2026 10:08:28 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Larry Richardson</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1770,24 +1762,24 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>0.574</v>
+        <v>0.593</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05/29/2026 8:13:59 AM</t>
+          <t>06/05/2026 8:46:40 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hunter McDowell</t>
+          <t>Rodney Salcido</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1798,13 +1790,13 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1819,6 +1811,137 @@
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>06/02/2026 3:36:18 PM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rodney Salcido</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>05/29/2026 12:01:35 PM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Leonard Ramirez</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>05/29/2026 8:13:59 AM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hunter McDowell</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Forward Collision Warning</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,15 +496,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/23/2026 8:26:38 PM</t>
+          <t>08/28/2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Justin Williams</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -513,7 +517,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -527,23 +531,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0.445</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/23/2026 3:17:23 PM</t>
+          <t>08/27/2026 2:09:55 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Colby Miller</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -552,7 +562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -566,27 +576,25 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N3" t="n">
+        <v>0.503</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/22/2026 3:40:00 PM</t>
+          <t>08/26/2026 3:03:24 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -597,7 +605,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -611,27 +619,25 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>0.396</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/19/2026 7:48:11 PM</t>
+          <t>08/23/2026 8:26:38 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Justin Williams</t>
-        </is>
-      </c>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -654,29 +660,23 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" t="n">
+        <v>0.445</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/18/2026 6:20:27 PM</t>
+          <t>08/23/2026 3:17:23 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Justin Williams</t>
-        </is>
-      </c>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/18/2026 6:29:37 AM</t>
+          <t>08/22/2026 3:40:00 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -745,24 +745,24 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>0.413</v>
+        <v>0.396</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/17/2026 5:16:19 PM</t>
+          <t>08/19/2026 7:48:11 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -787,25 +787,27 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0.441</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/13/2026 7:48:31 PM</t>
+          <t>08/18/2026 6:20:27 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colin Huff</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -816,7 +818,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -840,17 +842,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/12/2026 2:07:36 PM</t>
+          <t>08/18/2026 6:29:37 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -861,7 +863,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -875,27 +877,25 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N10" t="n">
+        <v>0.413</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/12/2026 9:16:59 AM</t>
+          <t>08/17/2026 5:16:19 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -921,24 +921,24 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>0.476</v>
+        <v>0.441</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/11/2026 6:39:58 PM</t>
+          <t>08/13/2026 7:48:31 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>641</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Colin Huff</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -963,15 +963,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>0.48</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/09/2026 11:31:56 AM</t>
+          <t>08/12/2026 2:07:36 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -992,7 +994,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1006,25 +1008,27 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>0.475</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/06/2026 5:42:43 PM</t>
+          <t>08/12/2026 9:16:59 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1035,7 +1039,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1049,27 +1053,25 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N14" t="n">
+        <v>0.476</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/05/2026 8:41:37 PM</t>
+          <t>08/11/2026 6:39:58 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1080,7 +1082,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1094,27 +1096,25 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N15" t="n">
+        <v>0.48</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/25/2026 9:55:54 AM</t>
+          <t>08/09/2026 11:31:56 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1139,27 +1139,25 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" t="n">
+        <v>0.475</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/22/2026 11:33:16 PM</t>
+          <t>08/06/2026 5:42:43 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1170,7 +1168,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1194,17 +1192,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/16/2026 8:34:56 PM</t>
+          <t>08/05/2026 8:41:37 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1215,7 +1213,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1239,7 +1237,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/14/2026 2:23:35 PM</t>
+          <t>07/25/2026 9:55:54 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1284,17 +1282,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/10/2026 2:59:56 PM</t>
+          <t>07/22/2026 11:33:16 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1305,7 +1303,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1319,25 +1317,27 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>5.626</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07/2026 11:46:28 AM</t>
+          <t>07/16/2026 8:34:56 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1372,17 +1372,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02/2026 12:16:01 PM</t>
+          <t>07/14/2026 2:23:35 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1407,25 +1407,27 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>0.656</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30/2026 4:21:07 AM</t>
+          <t>07/10/2026 2:59:56 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1436,13 +1438,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1450,17 +1452,15 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" t="n">
+        <v>5.626</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/18/2026 7:16:38 PM</t>
+          <t>07/07/2026 11:46:28 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>07/02/2026 12:16:01 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1540,27 +1540,25 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N25" t="n">
+        <v>0.656</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/16/2026 3:47:27 AM</t>
+          <t>06/30/2026 4:21:07 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1571,13 +1569,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1585,15 +1583,17 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>0.496</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/15/2026 2:31:48 PM</t>
+          <t>06/18/2026 7:16:38 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/12/2026 9:30:43 AM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1673,25 +1673,27 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>0.649</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/08/2026 7:17:58 PM</t>
+          <t>06/16/2026 3:47:27 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1702,7 +1704,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1716,27 +1718,25 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N29" t="n">
+        <v>0.496</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/07/2026 10:08:28 PM</t>
+          <t>06/15/2026 2:31:48 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Larry Richardson</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1761,25 +1761,27 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>0.593</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/05/2026 8:46:40 AM</t>
+          <t>06/12/2026 9:30:43 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1790,13 +1792,13 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1804,27 +1806,25 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N31" t="n">
+        <v>0.649</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/02/2026 3:36:18 PM</t>
+          <t>06/08/2026 7:17:58 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rodney Salcido</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1849,25 +1849,27 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>0.644</v>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05/29/2026 12:01:35 PM</t>
+          <t>06/07/2026 10:08:28 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Larry Richardson</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1893,24 +1895,24 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>0.574</v>
+        <v>0.593</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05/29/2026 8:13:59 AM</t>
+          <t>06/05/2026 8:46:40 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hunter McDowell</t>
+          <t>Rodney Salcido</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1921,13 +1923,13 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1942,6 +1944,49 @@
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>06/02/2026 3:36:18 PM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rodney Salcido</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HAAS Alert</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/28/2026 10:00:04 AM</t>
+          <t>09/02/2026 8:36:19 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>608</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Justin Williams</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -517,13 +517,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,17 +709,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/22/2026 3:40:00 PM</t>
+          <t>08/19/2026 7:48:11 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>517</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Justin Williams</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -744,25 +744,27 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>0.396</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/19/2026 7:48:11 PM</t>
+          <t>08/18/2026 6:29:37 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Justin Williams</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -773,7 +775,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -787,27 +789,25 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" t="n">
+        <v>0.413</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/18/2026 6:20:27 PM</t>
+          <t>08/17/2026 5:16:19 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Justin Williams</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -818,13 +818,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -832,27 +832,25 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" t="n">
+        <v>0.441</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/18/2026 6:29:37 AM</t>
+          <t>08/13/2026 7:48:31 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>641</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Colin Huff</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -863,7 +861,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -877,15 +875,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>0.413</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/17/2026 5:16:19 PM</t>
+          <t>08/12/2026 2:07:36 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -906,13 +906,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -920,25 +920,27 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0.441</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/13/2026 7:48:31 PM</t>
+          <t>08/12/2026 9:16:59 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colin Huff</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -949,7 +951,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -963,27 +965,25 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" t="n">
+        <v>0.476</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/12/2026 2:07:36 PM</t>
+          <t>08/11/2026 6:39:58 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1008,27 +1008,25 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" t="n">
+        <v>0.48</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/12/2026 9:16:59 AM</t>
+          <t>08/09/2026 11:31:56 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>606</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Fabian Velasco</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1039,13 +1037,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1054,24 +1052,24 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/11/2026 6:39:58 PM</t>
+          <t>08/06/2026 5:42:43 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1082,7 +1080,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1096,15 +1094,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0.48</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/09/2026 11:31:56 AM</t>
+          <t>08/05/2026 8:41:37 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1125,13 +1125,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1139,25 +1139,27 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0.475</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/06/2026 5:42:43 PM</t>
+          <t>07/25/2026 9:55:54 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1168,7 +1170,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1192,17 +1194,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/05/2026 8:41:37 PM</t>
+          <t>07/22/2026 11:33:16 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fabian Velasco</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1213,7 +1215,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1237,7 +1239,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/25/2026 9:55:54 AM</t>
+          <t>07/16/2026 8:34:56 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1282,17 +1284,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/22/2026 11:33:16 PM</t>
+          <t>07/14/2026 2:23:35 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>518</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Nathan Roe</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1303,7 +1305,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1327,17 +1329,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/16/2026 8:34:56 PM</t>
+          <t>07/10/2026 2:59:56 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1348,7 +1350,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1362,27 +1364,25 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" t="n">
+        <v>5.626</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/14/2026 2:23:35 PM</t>
+          <t>07/07/2026 11:46:28 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nathan Roe</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1417,17 +1417,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/10/2026 2:59:56 PM</t>
+          <t>07/02/2026 12:16:01 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1453,24 +1453,24 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>5.626</v>
+        <v>0.656</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07/2026 11:46:28 AM</t>
+          <t>06/30/2026 4:21:07 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Steve Perkins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1481,13 +1481,13 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02/2026 12:16:01 PM</t>
+          <t>06/18/2026 7:16:38 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1540,25 +1540,27 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>0.656</v>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30/2026 4:21:07 AM</t>
+          <t>06/17/2026 11:00:09 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Steve Perkins</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1569,13 +1571,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1593,17 +1595,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/18/2026 7:16:38 PM</t>
+          <t>06/16/2026 3:47:27 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Leonard Ramirez</t>
+          <t>Colby Miller</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1614,7 +1616,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1628,17 +1630,15 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" t="n">
+        <v>0.496</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/17/2026 11:00:09 AM</t>
+          <t>06/15/2026 2:31:48 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1683,17 +1683,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/16/2026 3:47:27 AM</t>
+          <t>06/12/2026 9:30:43 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colby Miller</t>
+          <t>Leonard Ramirez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1719,273 +1719,9 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>0.496</v>
+        <v>0.649</v>
       </c>
       <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>06/15/2026 2:31:48 PM</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Leonard Ramirez</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>HAAS Alert</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Camera Obstruction</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>06/12/2026 9:30:43 AM</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Leonard Ramirez</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>HAAS Alert</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Harsh Brake</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>06/08/2026 7:17:58 PM</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Leonard Ramirez</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>HAAS Alert</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>06/07/2026 10:08:28 PM</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Larry Richardson</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>HAAS Alert</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Harsh Brake</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>06/05/2026 8:46:40 AM</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Rodney Salcido</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>HAAS Alert</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Following Distance</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>06/02/2026 3:36:18 PM</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Rodney Salcido</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>HAAS Alert</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Harsh Brake</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Coached</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
